--- a/Draft/AUMAR - MO - 20250714.xlsx
+++ b/Draft/AUMAR - MO - 20250714.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muhammad.Nadeem\Documents\GitHub\AUMOR-AR\Draft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A44657B-259D-40FB-9AC7-DFA13F61D4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4EE56B-1B08-4233-984D-8EACFB6F1A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1596,7 +1596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1728,6 +1728,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5821,7 +5824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7459AA57-0E99-4794-B8C3-9A1F24D78F0B}" type="CELLRANGE">
+                    <a:fld id="{B7DB4733-EFBF-4AF2-A6A7-C1301937B4CA}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5830,7 +5833,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{48C635BF-2A66-4FAE-82F8-C9C2949CD48E}" type="SERIESNAME">
+                    <a:fld id="{36C4BFDB-235A-44B2-AFFF-688AD9F165A6}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -5864,7 +5867,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B412FF93-8661-4955-B428-6F96C238FB24}" type="CELLRANGE">
+                    <a:fld id="{E73B8211-FC2D-41E0-8057-7ED72EDF514F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5873,7 +5876,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{FBA020B3-8FFC-4B05-9F14-668642CB35CA}" type="SERIESNAME">
+                    <a:fld id="{C9E167F6-F8FC-4CF0-8931-96F91678281B}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -5907,7 +5910,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C93B8101-E1CC-4D9D-B3E8-12AB06493ECA}" type="CELLRANGE">
+                    <a:fld id="{4D507928-0666-4FB7-B999-E7F04ECDF268}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5916,7 +5919,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{6F16BCBB-ACE7-44E6-B099-407D421729D0}" type="SERIESNAME">
+                    <a:fld id="{AAB8CA43-902B-4D02-926C-DC35A9743BB1}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -5950,7 +5953,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{233AFF69-0AD5-400A-BE92-654F8921AF00}" type="CELLRANGE">
+                    <a:fld id="{17D42A27-CABB-404F-9324-262011ADB825}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5959,7 +5962,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{4221CA66-5B76-4EFA-B9C9-E0043F513772}" type="SERIESNAME">
+                    <a:fld id="{27170D7D-FFF2-4706-8786-0AA68D2A57AA}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -5993,7 +5996,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D579DD2-E679-4CD6-8F05-D3C1CCEFF8E8}" type="CELLRANGE">
+                    <a:fld id="{7B3AED2E-D705-45D0-BE13-2C4DDB224F2F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6002,7 +6005,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{1B6999BF-147C-4BEC-8A71-FFBED0A8B2BF}" type="SERIESNAME">
+                    <a:fld id="{32E861C2-832A-4B7D-8BDC-3219333AAC3E}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6036,7 +6039,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{185C6706-1BC9-4157-848E-316301CD705D}" type="CELLRANGE">
+                    <a:fld id="{8E576F22-E6B5-4D6F-A16B-631AD9D8DC87}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6045,7 +6048,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{5E6E65D6-9DA5-47B7-8623-C3D6480528AC}" type="SERIESNAME">
+                    <a:fld id="{47EF165C-A51E-4A0B-9B5D-00FAF9815905}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6079,7 +6082,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0A1D3B10-0FEC-4DCB-A271-220F1F108422}" type="CELLRANGE">
+                    <a:fld id="{57D7D555-125F-419F-B685-CEA4CB43AEF9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6088,7 +6091,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{1321F42C-125C-44D1-80E4-634A2665EDA0}" type="SERIESNAME">
+                    <a:fld id="{54BD71AE-E7F6-4B9D-9854-8CFCBC04C13E}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6676,7 +6679,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6AE2D8D4-69CD-4E11-A294-983C32B98BD3}" type="CELLRANGE">
+                    <a:fld id="{93B1D3FE-051C-4933-9D99-D26E124DA57A}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6685,7 +6688,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{38E59390-B9FB-4155-8F85-DAFBCB88EA35}" type="SERIESNAME">
+                    <a:fld id="{7761DF72-7643-4161-8196-539D0F4D4C31}" type="SERIESNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6718,7 +6721,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5A10B3F7-0CC8-4D2B-A27B-271E989EACD4}" type="CELLRANGE">
+                    <a:fld id="{42AD1262-8F78-43AC-8FEB-7C3D7C4C290A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6727,7 +6730,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{B2F0F391-D1F1-4A4E-8F49-34DE45604398}" type="SERIESNAME">
+                    <a:fld id="{444856F2-0C08-447D-84CD-5B6F53F0BA16}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6761,7 +6764,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B25D0F6D-4AD2-4ADC-AC24-1A431D108DB7}" type="CELLRANGE">
+                    <a:fld id="{4F52489A-FB9C-49AE-8303-E0EB71B583FC}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6770,7 +6773,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{72D993B9-1B1E-4D89-A728-96459A1B0105}" type="SERIESNAME">
+                    <a:fld id="{B1AB6811-104B-4562-9573-F8755B6BFA2E}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6804,7 +6807,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BBC5F470-FDE7-4357-AE85-B9AF05699953}" type="CELLRANGE">
+                    <a:fld id="{653D32EA-D2BF-4E3C-AE62-1B5E0470972B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6813,7 +6816,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{4DDE224B-DC1D-4F6A-9C92-DBFF3D53F498}" type="SERIESNAME">
+                    <a:fld id="{B093164C-67BD-454E-A562-30B1C540D59A}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6847,7 +6850,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4F65DB7B-ADB1-4A18-8AE3-2BC72835F1A3}" type="CELLRANGE">
+                    <a:fld id="{F9AFE00A-2FAE-40DE-BE74-C7395851CFE0}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6856,7 +6859,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{F64D5B04-E829-4A8A-94BF-7D9DDD30B556}" type="SERIESNAME">
+                    <a:fld id="{92C434F0-E49D-4741-B185-2B235FAC890A}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -6896,7 +6899,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC972C0D-B3CA-45FB-A366-385F98629DEB}" type="CELLRANGE">
+                    <a:fld id="{F19358A9-FD56-4E54-8F50-AE3DF82FB7E9}" type="CELLRANGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6905,7 +6908,7 @@
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{C6DAC1C9-32F3-41BD-B700-8C14F7208E64}" type="SERIESNAME">
+                    <a:fld id="{7E651540-6065-4FB6-80EF-71172AFE6187}" type="SERIESNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -7318,7 +7321,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5DB71123-0043-4C3B-9557-D52AEB68B845}" type="CELLRANGE">
+                    <a:fld id="{7AFB91DE-7053-4C80-89E3-D98824EE8CEC}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7327,7 +7330,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{B208C1F0-2ED7-4E0B-AD1A-63B5AC7AAEDD}" type="CATEGORYNAME">
+                    <a:fld id="{AFA69F6B-E4F2-4001-8506-CAD26B911847}" type="CATEGORYNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -7485,7 +7488,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5DCE4C48-ECC1-4191-AA1E-DF43ADFCF91E}" type="CELLRANGE">
+                    <a:fld id="{801E7C09-AE03-4AF2-B37D-DDECC61D55FF}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7494,7 +7497,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{EF5954BB-C907-4CF7-965C-F0AAB354DA3B}" type="CATEGORYNAME">
+                    <a:fld id="{A91A6D72-0F96-41E3-9BDE-73E675F32A5D}" type="CATEGORYNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -7652,7 +7655,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{239B48AF-97C9-4078-B1A4-71C0489B2349}" type="CELLRANGE">
+                    <a:fld id="{D774EBBE-A58D-495E-BD6A-F5B7D6B18152}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7661,7 +7664,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{C3586CE3-0A3D-498D-8F7D-CCC5CDF09841}" type="CATEGORYNAME">
+                    <a:fld id="{74B71261-599E-4360-B829-9AFA948F8885}" type="CATEGORYNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -7819,7 +7822,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{44138F5C-F9A1-4C4D-AA37-5E46118636F0}" type="CELLRANGE">
+                    <a:fld id="{F3372FDE-6971-4B0F-A8BF-2B8CEF616DDE}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7828,7 +7831,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{F5647158-44C6-4957-8318-C988E539B9C5}" type="CATEGORYNAME">
+                    <a:fld id="{6EBE31F2-03D3-4BFA-8C47-1CEDA2DA4C63}" type="CATEGORYNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -7986,7 +7989,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B8D4CAE1-7CC6-4D14-815F-7AD30485EBE3}" type="CELLRANGE">
+                    <a:fld id="{8008C43B-EAD0-48BF-A0C7-1A7B252BC90C}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7995,7 +7998,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{3D681FE3-EF80-4243-A774-0D1A9B25CFFE}" type="CATEGORYNAME">
+                    <a:fld id="{DFDDB2CB-181A-45B6-9512-00F478DD2EEF}" type="CATEGORYNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -8153,7 +8156,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8491D5C1-7C15-4033-9468-B5BBE69988C6}" type="CELLRANGE">
+                    <a:fld id="{2FBB0360-D8EB-4335-BBA1-525F85F9727F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8162,7 +8165,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{EBE5456E-7909-4CA6-A57C-FC38DFF75394}" type="CATEGORYNAME">
+                    <a:fld id="{F2A22DAF-8EA9-46C0-A9DA-EFB3DAC5EF51}" type="CATEGORYNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -9958,7 +9961,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C6AB1A40-D27C-4D0E-A9F9-FFAF9DDF5375}" type="CELLRANGE">
+                    <a:fld id="{502406C7-B6FF-4A20-AC15-0E0D96A687FE}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9967,7 +9970,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{D96090B5-84B3-40EC-91B4-6561EC044856}" type="SERIESNAME">
+                    <a:fld id="{E2BDCC0A-7982-44E1-910A-BDADA78440F7}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -10001,7 +10004,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D54AF7EB-63E6-4347-8B93-7252E2EF8DE6}" type="CELLRANGE">
+                    <a:fld id="{10BD91F8-9A54-4928-B070-DC2B95A77A99}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10010,7 +10013,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{A0D46E43-5712-4C0C-AEF5-DFE999D1F138}" type="SERIESNAME">
+                    <a:fld id="{ED2FC1A4-F983-4487-9DEB-9728DF1AD5B7}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -10044,7 +10047,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{140D17A1-6F3C-485C-B04F-17AC13AC4C4F}" type="CELLRANGE">
+                    <a:fld id="{348B2F68-FDFC-4C4B-8E47-BACAC721C4C0}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10053,7 +10056,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{4F0D022A-A091-4ABF-AF08-0185BA9F26AB}" type="SERIESNAME">
+                    <a:fld id="{26300C4F-6929-4CDD-8EE6-D90557AF64D7}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -10087,7 +10090,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E486FD4F-6630-4882-BF83-C79112B3953F}" type="CELLRANGE">
+                    <a:fld id="{961DE121-E11D-4797-A483-D9A906C47645}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10096,7 +10099,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{C20CB32D-1C13-4FF8-AD62-FC21FF8E2AC1}" type="SERIESNAME">
+                    <a:fld id="{645B8C7C-1D1D-43EA-833B-A3D7CED60A5B}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -10130,7 +10133,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6146D4DC-33CB-41DD-A51B-032C66287A93}" type="CELLRANGE">
+                    <a:fld id="{744EBF2A-0C1E-4C4F-9A16-D79DC91B2856}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10139,7 +10142,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{09698550-642B-47E7-9097-CA9007A60C5C}" type="SERIESNAME">
+                    <a:fld id="{801139EA-C01F-4C28-8D0A-771C9707DFA0}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -10173,7 +10176,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{22E38F56-01F7-4827-BCE0-0652A62645EC}" type="CELLRANGE">
+                    <a:fld id="{DAAA612F-A83D-4E7C-8511-B6C0DC3E430E}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10182,7 +10185,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{F6A96037-2D1B-4536-811B-F36EB85B1B81}" type="SERIESNAME">
+                    <a:fld id="{6F1DCFBC-0A6E-4EC3-8AEB-7E9646FAB5FA}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -11803,7 +11806,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ACC715BC-11AD-4ACD-9CDD-A6AE16935597}" type="CELLRANGE">
+                    <a:fld id="{0579E69E-69A0-49D3-AE35-5D9875928F28}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11812,7 +11815,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{69C8A503-389F-402B-AE70-7C7E87557C42}" type="SERIESNAME">
+                    <a:fld id="{A35BC236-D5A7-4C1A-95D0-3080227F1AEC}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -11846,7 +11849,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E34522FA-B75B-48B5-893D-819E69943E12}" type="CELLRANGE">
+                    <a:fld id="{251F9F27-EE3F-45F0-8076-35930EE52D2B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11855,7 +11858,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{0B0E8345-0ABC-47B3-94C2-CC3F3E3630DC}" type="SERIESNAME">
+                    <a:fld id="{C244A9E9-54A6-4718-81C7-112A0727D068}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -11889,7 +11892,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4BD1D057-A791-4606-A292-0EDB684BF2A7}" type="CELLRANGE">
+                    <a:fld id="{085576C2-AC4F-404B-95BB-E4F6C62C37B4}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11898,7 +11901,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{8EBB7F53-FA2F-4A24-9FAF-BE2A4FF21474}" type="SERIESNAME">
+                    <a:fld id="{DA009EEB-374E-46A1-AE49-FA0AACA72B34}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -11932,7 +11935,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{66DC7B4E-94CC-44BC-9676-F37D104FA3B3}" type="CELLRANGE">
+                    <a:fld id="{968B2E55-7D88-4AA3-8E4E-93CC08323BA8}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11941,7 +11944,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{4BACD29C-5ECD-4525-B98F-9AD1C82AF795}" type="SERIESNAME">
+                    <a:fld id="{C1CB1D06-05AB-460A-86AA-6DF89697D242}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -11975,7 +11978,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2771AAAC-D8DF-4013-AE2A-7622079F2284}" type="CELLRANGE">
+                    <a:fld id="{FD2F59AB-0902-457D-AA07-DC5C88185D35}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -11984,7 +11987,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{E8749427-8EC3-4C63-8082-B9E7DDC57040}" type="SERIESNAME">
+                    <a:fld id="{5A898B77-890D-4683-9473-682E608CA7C9}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12018,7 +12021,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37C98798-6772-487A-B11A-393B26C43CEA}" type="CELLRANGE">
+                    <a:fld id="{1F3AF80D-9719-40D3-9CA6-967C52397E9E}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12027,7 +12030,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{B7ADAD93-7DD7-42DB-8703-57C4A59DDC36}" type="SERIESNAME">
+                    <a:fld id="{B431962B-734C-4016-A0FF-2E5E25C64BB5}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12470,7 +12473,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{33240757-6C96-4D10-B7ED-CF134EEECF46}" type="CELLRANGE">
+                    <a:fld id="{F7D97539-7DE2-461B-910A-241B6E30F8A9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12479,7 +12482,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{FEFD4B95-AACE-4054-8310-50710FEF99F2}" type="SERIESNAME">
+                    <a:fld id="{E66F3B01-6371-4913-91BA-7CE0B9FFA11E}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12513,7 +12516,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51DD0300-3952-4538-AB79-4C46C0FFD24F}" type="CELLRANGE">
+                    <a:fld id="{AA508B33-0343-4624-AC08-4C39883061BE}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12522,7 +12525,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{0BA80210-3A6D-433F-B666-62BEC916122E}" type="SERIESNAME">
+                    <a:fld id="{82C2EF2E-D195-42A2-8DD8-93BD037E6FF8}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12556,7 +12559,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{134032BF-3B0B-4F02-8402-2B84EB333733}" type="CELLRANGE">
+                    <a:fld id="{F0750555-0305-4DAE-8244-1C7AD164F85F}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12565,7 +12568,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{89CC4147-FDB9-4C60-8BFE-443AAFAA32DB}" type="SERIESNAME">
+                    <a:fld id="{4A7952EE-95AC-44AD-9780-5ED86DE3489E}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12599,7 +12602,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A05D4C88-9E40-4DCB-8FDC-E9B9A7597128}" type="CELLRANGE">
+                    <a:fld id="{B6EE6556-1AC3-4FEF-9DDC-92AAD6A9F301}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12608,7 +12611,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{6BA3329B-AAB1-45BD-85E5-E782709CFC9F}" type="SERIESNAME">
+                    <a:fld id="{9C390F7F-0E31-401F-8609-5B8040536505}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12642,7 +12645,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD8F288B-78F6-472F-93EE-46B295ED25D4}" type="CELLRANGE">
+                    <a:fld id="{882D49CD-3775-4E06-9FF2-2C8503D8AD4A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12651,7 +12654,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{A7C0BBD9-DA9A-4E4D-BFE0-AA8921486678}" type="SERIESNAME">
+                    <a:fld id="{DE6D4319-BA93-469E-9AC8-9A1F7799DED9}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -12685,7 +12688,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{61D2AB40-989C-4001-A222-7C9C24B5D9C9}" type="CELLRANGE">
+                    <a:fld id="{8C127F4F-6A5A-4DB0-A2DE-96C130CA96F0}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -12694,7 +12697,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{69F9A2F4-6B29-425F-87EE-63A0CF413DE8}" type="SERIESNAME">
+                    <a:fld id="{E0119697-BC70-4896-A0A7-A093D23B0294}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13137,7 +13140,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFCC714A-DFCD-4DC4-B606-1553662F0637}" type="CELLRANGE">
+                    <a:fld id="{D34B2923-324F-4D41-B18A-865B0617B7D1}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13146,7 +13149,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{41BCEA6A-EE4D-4BEF-9D1D-70D1D00E3BC3}" type="SERIESNAME">
+                    <a:fld id="{0463F9B0-C0EF-40CB-AFC4-DA608ECE4D78}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13180,7 +13183,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1AF95373-F89D-4711-8A4F-BE53128DD012}" type="CELLRANGE">
+                    <a:fld id="{11BF679C-BB39-439A-8503-F12E8144760D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13189,7 +13192,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{985A5C12-1A11-4B69-B623-233AA09CA27A}" type="SERIESNAME">
+                    <a:fld id="{827DED83-3660-4B66-B9AD-C1DB96603513}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13223,7 +13226,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{75EDB559-E2E1-4DF5-867A-3E2F9DB0E794}" type="CELLRANGE">
+                    <a:fld id="{791A4F29-8FFB-496B-B68D-A131DE3AFA59}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13232,7 +13235,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{0352E10E-A00C-4B04-8850-EBCE93EB54A7}" type="SERIESNAME">
+                    <a:fld id="{1AC78DEA-DC55-45C0-8774-A6E4105BFD63}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13266,7 +13269,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{524B6504-6C78-4CD5-8282-EF7EC1447BCD}" type="CELLRANGE">
+                    <a:fld id="{DA4E6B97-D987-4C87-B9A2-39E5CEAEC3A4}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13275,7 +13278,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{3983782D-BA4A-4108-B858-DD1BC89C528A}" type="SERIESNAME">
+                    <a:fld id="{D6FDFAB9-9114-4A6F-87C6-B5A65B210F17}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13309,7 +13312,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9B6BD22F-3441-4604-9DBF-9713DA8D90B8}" type="CELLRANGE">
+                    <a:fld id="{DC637B6E-02C3-442F-9B5C-604D0FAF4C43}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13318,7 +13321,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{DD79E250-A134-427C-826D-163A363C3E24}" type="SERIESNAME">
+                    <a:fld id="{C02655F8-F247-4D1F-B376-A72559C115D1}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13352,7 +13355,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{993D0E2A-E73D-4602-9037-599469499CF7}" type="CELLRANGE">
+                    <a:fld id="{7F83C2D1-BA3B-4450-9C02-EE7D8F99FF86}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13361,7 +13364,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{43EF6E12-54AC-47AC-BB95-90DEB616A518}" type="SERIESNAME">
+                    <a:fld id="{9918D0FB-78D2-4D82-9F23-EE97D4A0AF12}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13803,7 +13806,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{16A94F4F-9264-4E19-9763-36B7BA1C0A4E}" type="CELLRANGE">
+                    <a:fld id="{802C80D8-E658-484A-8720-CD09D53E7125}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13812,7 +13815,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{43170FB7-4F4C-4BB5-B175-73F9A4876A17}" type="SERIESNAME">
+                    <a:fld id="{2076E772-9DB0-4089-9299-820006275519}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13846,7 +13849,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{276FE70B-003D-4A50-96E4-0D7F82BDD611}" type="CELLRANGE">
+                    <a:fld id="{DA9CFBB8-6CF9-4D8A-9CF8-DF79EC5CA5D9}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13855,7 +13858,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{859912F2-A7B5-424E-92BD-0998614CFFB1}" type="SERIESNAME">
+                    <a:fld id="{445F7696-1775-47D2-8B94-389E617EE3F0}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13889,7 +13892,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C72D1ED-6497-4024-A958-FD77E40D3D3D}" type="CELLRANGE">
+                    <a:fld id="{300DAB97-29EB-4CFA-8071-2B579AD0DCA3}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13898,7 +13901,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{3E5623FD-FAFD-49A4-B37E-2734BBACE351}" type="SERIESNAME">
+                    <a:fld id="{257B9F0E-3396-4B67-825A-1DCEAE8685DA}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13932,7 +13935,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{644BFB0E-1ED3-4F03-8BB6-3675AE0ADB72}" type="CELLRANGE">
+                    <a:fld id="{D6111AD9-E468-4016-A52E-36E66E7CF012}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13941,7 +13944,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{74D9F62F-23EF-4011-9139-2B9C265D9629}" type="SERIESNAME">
+                    <a:fld id="{60DE72BC-72B7-49AF-9BCB-DFDA174BAEE7}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -13975,7 +13978,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{790E525D-8F22-4803-98B7-536DF1DE5EA5}" type="CELLRANGE">
+                    <a:fld id="{3728B416-5015-4276-89B0-005432491FB8}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13984,7 +13987,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{5EE49E1D-93E9-412B-82F4-54CA8D01FADA}" type="SERIESNAME">
+                    <a:fld id="{6E7F06C4-06A7-4A1E-94FB-EA6DCEA9AB2C}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -14018,7 +14021,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9CD369D-0FE2-44D4-A559-8A25CCBA0496}" type="CELLRANGE">
+                    <a:fld id="{682C9B5F-85EB-4C5A-B4C9-193622621465}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14027,7 +14030,7 @@
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:t> </a:t>
                     </a:r>
-                    <a:fld id="{9DABAE9D-DA1D-4D42-A0EE-98812B2A1635}" type="SERIESNAME">
+                    <a:fld id="{D30F07EF-B74C-43DC-BE7D-D29A58B748E1}" type="SERIESNAME">
                       <a:rPr lang="en-GB" baseline="0"/>
                       <a:pPr/>
                       <a:t>[SERIES NAME]</a:t>
@@ -35311,16 +35314,16 @@
       <c r="Q4" s="6">
         <v>4</v>
       </c>
-      <c r="R4" s="6">
-        <v>4</v>
-      </c>
-      <c r="S4" s="6">
-        <v>4</v>
-      </c>
-      <c r="T4" s="6">
-        <v>4</v>
-      </c>
-      <c r="U4" s="6">
+      <c r="R4" s="48">
+        <v>4</v>
+      </c>
+      <c r="S4" s="48">
+        <v>4</v>
+      </c>
+      <c r="T4" s="48">
+        <v>4</v>
+      </c>
+      <c r="U4" s="48">
         <v>4</v>
       </c>
       <c r="V4" s="6">
@@ -35400,16 +35403,16 @@
       <c r="Q5" s="6">
         <v>2</v>
       </c>
-      <c r="R5" s="6">
-        <v>4</v>
-      </c>
-      <c r="S5" s="6">
-        <v>4</v>
-      </c>
-      <c r="T5" s="6">
+      <c r="R5" s="48">
+        <v>4</v>
+      </c>
+      <c r="S5" s="48">
+        <v>4</v>
+      </c>
+      <c r="T5" s="48">
         <v>5</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="48">
         <v>4</v>
       </c>
       <c r="V5" s="6">
@@ -35489,16 +35492,16 @@
       <c r="Q6" s="6">
         <v>2</v>
       </c>
-      <c r="R6" s="6">
-        <v>4</v>
-      </c>
-      <c r="S6" s="6">
-        <v>4</v>
-      </c>
-      <c r="T6" s="6">
-        <v>4</v>
-      </c>
-      <c r="U6" s="6">
+      <c r="R6" s="48">
+        <v>4</v>
+      </c>
+      <c r="S6" s="48">
+        <v>4</v>
+      </c>
+      <c r="T6" s="48">
+        <v>4</v>
+      </c>
+      <c r="U6" s="48">
         <v>4</v>
       </c>
       <c r="V6" s="6">
@@ -35578,16 +35581,16 @@
       <c r="Q7" s="6">
         <v>2</v>
       </c>
-      <c r="R7" s="6">
-        <v>3</v>
-      </c>
-      <c r="S7" s="6">
-        <v>4</v>
-      </c>
-      <c r="T7" s="6">
-        <v>4</v>
-      </c>
-      <c r="U7" s="6">
+      <c r="R7" s="48">
+        <v>3</v>
+      </c>
+      <c r="S7" s="48">
+        <v>4</v>
+      </c>
+      <c r="T7" s="48">
+        <v>4</v>
+      </c>
+      <c r="U7" s="48">
         <v>4</v>
       </c>
       <c r="V7" s="6">
@@ -35667,16 +35670,16 @@
       <c r="Q8" s="6">
         <v>2</v>
       </c>
-      <c r="R8" s="6">
+      <c r="R8" s="48">
         <v>5</v>
       </c>
-      <c r="S8" s="6">
-        <v>4</v>
-      </c>
-      <c r="T8" s="6">
-        <v>4</v>
-      </c>
-      <c r="U8" s="6">
+      <c r="S8" s="48">
+        <v>4</v>
+      </c>
+      <c r="T8" s="48">
+        <v>4</v>
+      </c>
+      <c r="U8" s="48">
         <v>4</v>
       </c>
       <c r="V8" s="6">
@@ -35756,16 +35759,16 @@
       <c r="Q9" s="6">
         <v>1</v>
       </c>
-      <c r="R9" s="6">
-        <v>4</v>
-      </c>
-      <c r="S9" s="6">
-        <v>4</v>
-      </c>
-      <c r="T9" s="6">
-        <v>4</v>
-      </c>
-      <c r="U9" s="6">
+      <c r="R9" s="48">
+        <v>4</v>
+      </c>
+      <c r="S9" s="48">
+        <v>4</v>
+      </c>
+      <c r="T9" s="48">
+        <v>4</v>
+      </c>
+      <c r="U9" s="48">
         <v>4</v>
       </c>
       <c r="V9" s="6">
@@ -35845,16 +35848,16 @@
       <c r="Q10" s="6">
         <v>4</v>
       </c>
-      <c r="R10" s="6">
-        <v>4</v>
-      </c>
-      <c r="S10" s="6">
-        <v>4</v>
-      </c>
-      <c r="T10" s="6">
-        <v>4</v>
-      </c>
-      <c r="U10" s="6">
+      <c r="R10" s="48">
+        <v>4</v>
+      </c>
+      <c r="S10" s="48">
+        <v>4</v>
+      </c>
+      <c r="T10" s="48">
+        <v>4</v>
+      </c>
+      <c r="U10" s="48">
         <v>4</v>
       </c>
       <c r="V10" s="6">
@@ -35934,16 +35937,16 @@
       <c r="Q11" s="6">
         <v>4</v>
       </c>
-      <c r="R11" s="6">
-        <v>4</v>
-      </c>
-      <c r="S11" s="6">
-        <v>4</v>
-      </c>
-      <c r="T11" s="6">
-        <v>3</v>
-      </c>
-      <c r="U11" s="6">
+      <c r="R11" s="48">
+        <v>4</v>
+      </c>
+      <c r="S11" s="48">
+        <v>4</v>
+      </c>
+      <c r="T11" s="48">
+        <v>3</v>
+      </c>
+      <c r="U11" s="48">
         <v>3</v>
       </c>
       <c r="V11" s="6">
@@ -36023,16 +36026,16 @@
       <c r="Q12" s="6">
         <v>3</v>
       </c>
-      <c r="R12" s="6">
-        <v>3</v>
-      </c>
-      <c r="S12" s="6">
-        <v>3</v>
-      </c>
-      <c r="T12" s="6">
-        <v>3</v>
-      </c>
-      <c r="U12" s="6">
+      <c r="R12" s="48">
+        <v>3</v>
+      </c>
+      <c r="S12" s="48">
+        <v>3</v>
+      </c>
+      <c r="T12" s="48">
+        <v>3</v>
+      </c>
+      <c r="U12" s="48">
         <v>3</v>
       </c>
       <c r="V12" s="6">
@@ -36112,16 +36115,16 @@
       <c r="Q13" s="6">
         <v>3</v>
       </c>
-      <c r="R13" s="6">
-        <v>3</v>
-      </c>
-      <c r="S13" s="6">
-        <v>3</v>
-      </c>
-      <c r="T13" s="6">
-        <v>3</v>
-      </c>
-      <c r="U13" s="6">
+      <c r="R13" s="48">
+        <v>3</v>
+      </c>
+      <c r="S13" s="48">
+        <v>3</v>
+      </c>
+      <c r="T13" s="48">
+        <v>3</v>
+      </c>
+      <c r="U13" s="48">
         <v>3</v>
       </c>
       <c r="V13" s="6">
@@ -36201,16 +36204,16 @@
       <c r="Q14" s="6">
         <v>3</v>
       </c>
-      <c r="R14" s="6">
-        <v>3</v>
-      </c>
-      <c r="S14" s="6">
-        <v>3</v>
-      </c>
-      <c r="T14" s="6">
-        <v>3</v>
-      </c>
-      <c r="U14" s="6">
+      <c r="R14" s="48">
+        <v>3</v>
+      </c>
+      <c r="S14" s="48">
+        <v>3</v>
+      </c>
+      <c r="T14" s="48">
+        <v>3</v>
+      </c>
+      <c r="U14" s="48">
         <v>3</v>
       </c>
       <c r="V14" s="6">
@@ -36290,16 +36293,16 @@
       <c r="Q15" s="6">
         <v>2</v>
       </c>
-      <c r="R15" s="6">
-        <v>4</v>
-      </c>
-      <c r="S15" s="6">
-        <v>3</v>
-      </c>
-      <c r="T15" s="6">
-        <v>4</v>
-      </c>
-      <c r="U15" s="6">
+      <c r="R15" s="48">
+        <v>4</v>
+      </c>
+      <c r="S15" s="48">
+        <v>3</v>
+      </c>
+      <c r="T15" s="48">
+        <v>4</v>
+      </c>
+      <c r="U15" s="48">
         <v>4</v>
       </c>
       <c r="V15" s="6">
@@ -36379,16 +36382,16 @@
       <c r="Q16" s="6">
         <v>2</v>
       </c>
-      <c r="R16" s="6">
-        <v>4</v>
-      </c>
-      <c r="S16" s="6">
-        <v>4</v>
-      </c>
-      <c r="T16" s="6">
-        <v>4</v>
-      </c>
-      <c r="U16" s="6">
+      <c r="R16" s="48">
+        <v>4</v>
+      </c>
+      <c r="S16" s="48">
+        <v>4</v>
+      </c>
+      <c r="T16" s="48">
+        <v>4</v>
+      </c>
+      <c r="U16" s="48">
         <v>4</v>
       </c>
       <c r="V16" s="6">
@@ -36468,16 +36471,16 @@
       <c r="Q17" s="6">
         <v>3</v>
       </c>
-      <c r="R17" s="6">
-        <v>4</v>
-      </c>
-      <c r="S17" s="6">
-        <v>4</v>
-      </c>
-      <c r="T17" s="6">
-        <v>4</v>
-      </c>
-      <c r="U17" s="6">
+      <c r="R17" s="48">
+        <v>4</v>
+      </c>
+      <c r="S17" s="48">
+        <v>4</v>
+      </c>
+      <c r="T17" s="48">
+        <v>4</v>
+      </c>
+      <c r="U17" s="48">
         <v>4</v>
       </c>
       <c r="V17" s="6">
@@ -36557,16 +36560,16 @@
       <c r="Q18" s="6">
         <v>1</v>
       </c>
-      <c r="R18" s="6">
+      <c r="R18" s="48">
         <v>5</v>
       </c>
-      <c r="S18" s="6">
+      <c r="S18" s="48">
         <v>1</v>
       </c>
-      <c r="T18" s="6">
+      <c r="T18" s="48">
         <v>5</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U18" s="48">
         <v>5</v>
       </c>
       <c r="V18" s="6">
@@ -36646,16 +36649,16 @@
       <c r="Q19" s="6">
         <v>1</v>
       </c>
-      <c r="R19" s="6">
+      <c r="R19" s="48">
         <v>1</v>
       </c>
-      <c r="S19" s="6">
+      <c r="S19" s="48">
         <v>1</v>
       </c>
-      <c r="T19" s="6">
+      <c r="T19" s="48">
         <v>1</v>
       </c>
-      <c r="U19" s="6">
+      <c r="U19" s="48">
         <v>1</v>
       </c>
       <c r="V19" s="6">
@@ -36735,16 +36738,16 @@
       <c r="Q20" s="6">
         <v>3</v>
       </c>
-      <c r="R20" s="6">
-        <v>3</v>
-      </c>
-      <c r="S20" s="6">
-        <v>3</v>
-      </c>
-      <c r="T20" s="6">
-        <v>3</v>
-      </c>
-      <c r="U20" s="6">
+      <c r="R20" s="48">
+        <v>3</v>
+      </c>
+      <c r="S20" s="48">
+        <v>3</v>
+      </c>
+      <c r="T20" s="48">
+        <v>3</v>
+      </c>
+      <c r="U20" s="48">
         <v>3</v>
       </c>
       <c r="V20" s="6">
@@ -36824,16 +36827,16 @@
       <c r="Q21" s="6">
         <v>3</v>
       </c>
-      <c r="R21" s="6">
-        <v>4</v>
-      </c>
-      <c r="S21" s="6">
-        <v>4</v>
-      </c>
-      <c r="T21" s="6">
-        <v>3</v>
-      </c>
-      <c r="U21" s="6">
+      <c r="R21" s="48">
+        <v>4</v>
+      </c>
+      <c r="S21" s="48">
+        <v>4</v>
+      </c>
+      <c r="T21" s="48">
+        <v>3</v>
+      </c>
+      <c r="U21" s="48">
         <v>4</v>
       </c>
       <c r="V21" s="6">
@@ -36913,16 +36916,16 @@
       <c r="Q22" s="6">
         <v>3</v>
       </c>
-      <c r="R22" s="6">
-        <v>3</v>
-      </c>
-      <c r="S22" s="6">
-        <v>3</v>
-      </c>
-      <c r="T22" s="6">
-        <v>3</v>
-      </c>
-      <c r="U22" s="6">
+      <c r="R22" s="48">
+        <v>3</v>
+      </c>
+      <c r="S22" s="48">
+        <v>3</v>
+      </c>
+      <c r="T22" s="48">
+        <v>3</v>
+      </c>
+      <c r="U22" s="48">
         <v>3</v>
       </c>
       <c r="V22" s="6">
@@ -37002,16 +37005,16 @@
       <c r="Q23" s="6">
         <v>3</v>
       </c>
-      <c r="R23" s="6">
-        <v>3</v>
-      </c>
-      <c r="S23" s="6">
-        <v>3</v>
-      </c>
-      <c r="T23" s="6">
-        <v>4</v>
-      </c>
-      <c r="U23" s="6">
+      <c r="R23" s="48">
+        <v>3</v>
+      </c>
+      <c r="S23" s="48">
+        <v>3</v>
+      </c>
+      <c r="T23" s="48">
+        <v>4</v>
+      </c>
+      <c r="U23" s="48">
         <v>4</v>
       </c>
       <c r="V23" s="6">
@@ -37091,16 +37094,16 @@
       <c r="Q24" s="6">
         <v>2</v>
       </c>
-      <c r="R24" s="6">
-        <v>4</v>
-      </c>
-      <c r="S24" s="6">
-        <v>4</v>
-      </c>
-      <c r="T24" s="6">
+      <c r="R24" s="48">
+        <v>4</v>
+      </c>
+      <c r="S24" s="48">
+        <v>4</v>
+      </c>
+      <c r="T24" s="48">
         <v>5</v>
       </c>
-      <c r="U24" s="6">
+      <c r="U24" s="48">
         <v>4</v>
       </c>
       <c r="V24" s="6">
@@ -37180,16 +37183,16 @@
       <c r="Q25" s="6">
         <v>4</v>
       </c>
-      <c r="R25" s="6">
-        <v>4</v>
-      </c>
-      <c r="S25" s="6">
-        <v>4</v>
-      </c>
-      <c r="T25" s="6">
-        <v>4</v>
-      </c>
-      <c r="U25" s="6">
+      <c r="R25" s="48">
+        <v>4</v>
+      </c>
+      <c r="S25" s="48">
+        <v>4</v>
+      </c>
+      <c r="T25" s="48">
+        <v>4</v>
+      </c>
+      <c r="U25" s="48">
         <v>4</v>
       </c>
       <c r="V25" s="6">
@@ -37269,16 +37272,16 @@
       <c r="Q26" s="6">
         <v>3</v>
       </c>
-      <c r="R26" s="6">
-        <v>3</v>
-      </c>
-      <c r="S26" s="6">
-        <v>3</v>
-      </c>
-      <c r="T26" s="6">
-        <v>4</v>
-      </c>
-      <c r="U26" s="6">
+      <c r="R26" s="48">
+        <v>3</v>
+      </c>
+      <c r="S26" s="48">
+        <v>3</v>
+      </c>
+      <c r="T26" s="48">
+        <v>4</v>
+      </c>
+      <c r="U26" s="48">
         <v>3</v>
       </c>
       <c r="V26" s="6">
@@ -37358,16 +37361,16 @@
       <c r="Q27" s="6">
         <v>1</v>
       </c>
-      <c r="R27" s="6">
-        <v>4</v>
-      </c>
-      <c r="S27" s="6">
-        <v>3</v>
-      </c>
-      <c r="T27" s="6">
-        <v>4</v>
-      </c>
-      <c r="U27" s="6">
+      <c r="R27" s="48">
+        <v>4</v>
+      </c>
+      <c r="S27" s="48">
+        <v>3</v>
+      </c>
+      <c r="T27" s="48">
+        <v>4</v>
+      </c>
+      <c r="U27" s="48">
         <v>5</v>
       </c>
       <c r="V27" s="6">
@@ -37447,16 +37450,16 @@
       <c r="Q28" s="6">
         <v>2</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R28" s="48">
         <v>5</v>
       </c>
-      <c r="S28" s="6">
-        <v>4</v>
-      </c>
-      <c r="T28" s="6">
-        <v>4</v>
-      </c>
-      <c r="U28" s="6">
+      <c r="S28" s="48">
+        <v>4</v>
+      </c>
+      <c r="T28" s="48">
+        <v>4</v>
+      </c>
+      <c r="U28" s="48">
         <v>3</v>
       </c>
       <c r="V28" s="6">
@@ -37536,16 +37539,16 @@
       <c r="Q29" s="6">
         <v>2</v>
       </c>
-      <c r="R29" s="6">
-        <v>4</v>
-      </c>
-      <c r="S29" s="6">
+      <c r="R29" s="48">
+        <v>4</v>
+      </c>
+      <c r="S29" s="48">
         <v>5</v>
       </c>
-      <c r="T29" s="6">
+      <c r="T29" s="48">
         <v>5</v>
       </c>
-      <c r="U29" s="6">
+      <c r="U29" s="48">
         <v>5</v>
       </c>
       <c r="V29" s="6">
@@ -37625,16 +37628,16 @@
       <c r="Q30" s="6">
         <v>2</v>
       </c>
-      <c r="R30" s="6">
+      <c r="R30" s="48">
         <v>5</v>
       </c>
-      <c r="S30" s="6">
-        <v>4</v>
-      </c>
-      <c r="T30" s="6">
-        <v>4</v>
-      </c>
-      <c r="U30" s="6">
+      <c r="S30" s="48">
+        <v>4</v>
+      </c>
+      <c r="T30" s="48">
+        <v>4</v>
+      </c>
+      <c r="U30" s="48">
         <v>4</v>
       </c>
       <c r="V30" s="6">
@@ -37711,16 +37714,16 @@
       <c r="Q31" s="6">
         <v>3</v>
       </c>
-      <c r="R31" s="6">
-        <v>4</v>
-      </c>
-      <c r="S31" s="6">
-        <v>3</v>
-      </c>
-      <c r="T31" s="6">
-        <v>4</v>
-      </c>
-      <c r="U31" s="6">
+      <c r="R31" s="48">
+        <v>4</v>
+      </c>
+      <c r="S31" s="48">
+        <v>3</v>
+      </c>
+      <c r="T31" s="48">
+        <v>4</v>
+      </c>
+      <c r="U31" s="48">
         <v>4</v>
       </c>
       <c r="V31" s="6">
@@ -37800,16 +37803,16 @@
       <c r="Q32" s="6">
         <v>2</v>
       </c>
-      <c r="R32" s="6">
+      <c r="R32" s="48">
         <v>5</v>
       </c>
-      <c r="S32" s="6">
-        <v>4</v>
-      </c>
-      <c r="T32" s="6">
-        <v>3</v>
-      </c>
-      <c r="U32" s="6">
+      <c r="S32" s="48">
+        <v>4</v>
+      </c>
+      <c r="T32" s="48">
+        <v>3</v>
+      </c>
+      <c r="U32" s="48">
         <v>3</v>
       </c>
       <c r="V32" s="6">
@@ -37889,16 +37892,16 @@
       <c r="Q33" s="6">
         <v>2</v>
       </c>
-      <c r="R33" s="6">
-        <v>4</v>
-      </c>
-      <c r="S33" s="6">
-        <v>4</v>
-      </c>
-      <c r="T33" s="6">
-        <v>4</v>
-      </c>
-      <c r="U33" s="6">
+      <c r="R33" s="48">
+        <v>4</v>
+      </c>
+      <c r="S33" s="48">
+        <v>4</v>
+      </c>
+      <c r="T33" s="48">
+        <v>4</v>
+      </c>
+      <c r="U33" s="48">
         <v>4</v>
       </c>
       <c r="V33" s="6">
@@ -37978,16 +37981,16 @@
       <c r="Q34" s="6">
         <v>2</v>
       </c>
-      <c r="R34" s="6">
+      <c r="R34" s="48">
         <v>5</v>
       </c>
-      <c r="S34" s="6">
-        <v>4</v>
-      </c>
-      <c r="T34" s="6">
-        <v>4</v>
-      </c>
-      <c r="U34" s="6">
+      <c r="S34" s="48">
+        <v>4</v>
+      </c>
+      <c r="T34" s="48">
+        <v>4</v>
+      </c>
+      <c r="U34" s="48">
         <v>5</v>
       </c>
       <c r="V34" s="6">
@@ -38067,16 +38070,16 @@
       <c r="Q35" s="6">
         <v>2</v>
       </c>
-      <c r="R35" s="6">
-        <v>4</v>
-      </c>
-      <c r="S35" s="6">
-        <v>4</v>
-      </c>
-      <c r="T35" s="6">
-        <v>4</v>
-      </c>
-      <c r="U35" s="6">
+      <c r="R35" s="48">
+        <v>4</v>
+      </c>
+      <c r="S35" s="48">
+        <v>4</v>
+      </c>
+      <c r="T35" s="48">
+        <v>4</v>
+      </c>
+      <c r="U35" s="48">
         <v>4</v>
       </c>
       <c r="V35" s="6">
@@ -38156,16 +38159,16 @@
       <c r="Q36" s="6">
         <v>2</v>
       </c>
-      <c r="R36" s="6">
-        <v>4</v>
-      </c>
-      <c r="S36" s="6">
-        <v>3</v>
-      </c>
-      <c r="T36" s="6">
-        <v>3</v>
-      </c>
-      <c r="U36" s="6">
+      <c r="R36" s="48">
+        <v>4</v>
+      </c>
+      <c r="S36" s="48">
+        <v>3</v>
+      </c>
+      <c r="T36" s="48">
+        <v>3</v>
+      </c>
+      <c r="U36" s="48">
         <v>2</v>
       </c>
       <c r="V36" s="6">
@@ -38245,16 +38248,16 @@
       <c r="Q37" s="6">
         <v>3</v>
       </c>
-      <c r="R37" s="6">
+      <c r="R37" s="48">
         <v>1</v>
       </c>
-      <c r="S37" s="6">
+      <c r="S37" s="48">
         <v>2</v>
       </c>
-      <c r="T37" s="6">
-        <v>4</v>
-      </c>
-      <c r="U37" s="6">
+      <c r="T37" s="48">
+        <v>4</v>
+      </c>
+      <c r="U37" s="48">
         <v>3</v>
       </c>
       <c r="V37" s="6">
@@ -38334,16 +38337,16 @@
       <c r="Q38" s="6">
         <v>2</v>
       </c>
-      <c r="R38" s="6">
-        <v>3</v>
-      </c>
-      <c r="S38" s="6">
-        <v>3</v>
-      </c>
-      <c r="T38" s="6">
-        <v>4</v>
-      </c>
-      <c r="U38" s="6">
+      <c r="R38" s="48">
+        <v>3</v>
+      </c>
+      <c r="S38" s="48">
+        <v>3</v>
+      </c>
+      <c r="T38" s="48">
+        <v>4</v>
+      </c>
+      <c r="U38" s="48">
         <v>4</v>
       </c>
       <c r="V38" s="6">
@@ -38423,16 +38426,16 @@
       <c r="Q39" s="6">
         <v>3</v>
       </c>
-      <c r="R39" s="6">
-        <v>3</v>
-      </c>
-      <c r="S39" s="6">
-        <v>3</v>
-      </c>
-      <c r="T39" s="6">
-        <v>3</v>
-      </c>
-      <c r="U39" s="6">
+      <c r="R39" s="48">
+        <v>3</v>
+      </c>
+      <c r="S39" s="48">
+        <v>3</v>
+      </c>
+      <c r="T39" s="48">
+        <v>3</v>
+      </c>
+      <c r="U39" s="48">
         <v>3</v>
       </c>
       <c r="V39" s="6">
@@ -38512,16 +38515,16 @@
       <c r="Q40" s="6">
         <v>3</v>
       </c>
-      <c r="R40" s="6">
-        <v>4</v>
-      </c>
-      <c r="S40" s="6">
-        <v>4</v>
-      </c>
-      <c r="T40" s="6">
-        <v>4</v>
-      </c>
-      <c r="U40" s="6">
+      <c r="R40" s="48">
+        <v>4</v>
+      </c>
+      <c r="S40" s="48">
+        <v>4</v>
+      </c>
+      <c r="T40" s="48">
+        <v>4</v>
+      </c>
+      <c r="U40" s="48">
         <v>3</v>
       </c>
       <c r="V40" s="6">
@@ -38601,16 +38604,16 @@
       <c r="Q41" s="6">
         <v>1</v>
       </c>
-      <c r="R41" s="6">
+      <c r="R41" s="48">
         <v>1</v>
       </c>
-      <c r="S41" s="6">
+      <c r="S41" s="48">
         <v>1</v>
       </c>
-      <c r="T41" s="6">
+      <c r="T41" s="48">
         <v>1</v>
       </c>
-      <c r="U41" s="6">
+      <c r="U41" s="48">
         <v>1</v>
       </c>
       <c r="V41" s="6">
@@ -38690,16 +38693,16 @@
       <c r="Q42" s="6">
         <v>3</v>
       </c>
-      <c r="R42" s="6">
-        <v>4</v>
-      </c>
-      <c r="S42" s="6">
-        <v>3</v>
-      </c>
-      <c r="T42" s="6">
-        <v>4</v>
-      </c>
-      <c r="U42" s="6">
+      <c r="R42" s="48">
+        <v>4</v>
+      </c>
+      <c r="S42" s="48">
+        <v>3</v>
+      </c>
+      <c r="T42" s="48">
+        <v>4</v>
+      </c>
+      <c r="U42" s="48">
         <v>3</v>
       </c>
       <c r="V42" s="6">
@@ -38779,16 +38782,16 @@
       <c r="Q43" s="6">
         <v>5</v>
       </c>
-      <c r="R43" s="6">
-        <v>4</v>
-      </c>
-      <c r="S43" s="6">
+      <c r="R43" s="48">
+        <v>4</v>
+      </c>
+      <c r="S43" s="48">
         <v>5</v>
       </c>
-      <c r="T43" s="6">
-        <v>4</v>
-      </c>
-      <c r="U43" s="6">
+      <c r="T43" s="48">
+        <v>4</v>
+      </c>
+      <c r="U43" s="48">
         <v>4</v>
       </c>
       <c r="V43" s="6">
@@ -38868,16 +38871,16 @@
       <c r="Q44" s="6">
         <v>2</v>
       </c>
-      <c r="R44" s="6">
+      <c r="R44" s="48">
         <v>5</v>
       </c>
-      <c r="S44" s="6">
-        <v>3</v>
-      </c>
-      <c r="T44" s="6">
+      <c r="S44" s="48">
+        <v>3</v>
+      </c>
+      <c r="T44" s="48">
         <v>5</v>
       </c>
-      <c r="U44" s="6">
+      <c r="U44" s="48">
         <v>3</v>
       </c>
       <c r="V44" s="6">
@@ -38957,16 +38960,16 @@
       <c r="Q45" s="6">
         <v>4</v>
       </c>
-      <c r="R45" s="6">
+      <c r="R45" s="48">
         <v>5</v>
       </c>
-      <c r="S45" s="6">
+      <c r="S45" s="48">
         <v>5</v>
       </c>
-      <c r="T45" s="6">
-        <v>4</v>
-      </c>
-      <c r="U45" s="6">
+      <c r="T45" s="48">
+        <v>4</v>
+      </c>
+      <c r="U45" s="48">
         <v>4</v>
       </c>
       <c r="V45" s="6">
@@ -39046,16 +39049,16 @@
       <c r="Q46" s="6">
         <v>4</v>
       </c>
-      <c r="R46" s="6">
-        <v>4</v>
-      </c>
-      <c r="S46" s="6">
+      <c r="R46" s="48">
+        <v>4</v>
+      </c>
+      <c r="S46" s="48">
         <v>5</v>
       </c>
-      <c r="T46" s="6">
-        <v>4</v>
-      </c>
-      <c r="U46" s="6">
+      <c r="T46" s="48">
+        <v>4</v>
+      </c>
+      <c r="U46" s="48">
         <v>5</v>
       </c>
       <c r="V46" s="6">
@@ -39135,16 +39138,16 @@
       <c r="Q47" s="6">
         <v>1</v>
       </c>
-      <c r="R47" s="6">
+      <c r="R47" s="48">
         <v>5</v>
       </c>
-      <c r="S47" s="6">
-        <v>4</v>
-      </c>
-      <c r="T47" s="6">
+      <c r="S47" s="48">
+        <v>4</v>
+      </c>
+      <c r="T47" s="48">
         <v>5</v>
       </c>
-      <c r="U47" s="6">
+      <c r="U47" s="48">
         <v>3</v>
       </c>
       <c r="V47" s="6">
@@ -39224,16 +39227,16 @@
       <c r="Q48" s="6">
         <v>3</v>
       </c>
-      <c r="R48" s="6">
-        <v>3</v>
-      </c>
-      <c r="S48" s="6">
-        <v>3</v>
-      </c>
-      <c r="T48" s="6">
-        <v>4</v>
-      </c>
-      <c r="U48" s="6">
+      <c r="R48" s="48">
+        <v>3</v>
+      </c>
+      <c r="S48" s="48">
+        <v>3</v>
+      </c>
+      <c r="T48" s="48">
+        <v>4</v>
+      </c>
+      <c r="U48" s="48">
         <v>3</v>
       </c>
       <c r="V48" s="6">
@@ -39313,16 +39316,16 @@
       <c r="Q49" s="6">
         <v>5</v>
       </c>
-      <c r="R49" s="6">
-        <v>4</v>
-      </c>
-      <c r="S49" s="6">
-        <v>4</v>
-      </c>
-      <c r="T49" s="6">
-        <v>3</v>
-      </c>
-      <c r="U49" s="6">
+      <c r="R49" s="48">
+        <v>4</v>
+      </c>
+      <c r="S49" s="48">
+        <v>4</v>
+      </c>
+      <c r="T49" s="48">
+        <v>3</v>
+      </c>
+      <c r="U49" s="48">
         <v>3</v>
       </c>
       <c r="V49" s="6">
@@ -39402,16 +39405,16 @@
       <c r="Q50" s="6">
         <v>1</v>
       </c>
-      <c r="R50" s="6">
-        <v>4</v>
-      </c>
-      <c r="S50" s="6">
+      <c r="R50" s="48">
+        <v>4</v>
+      </c>
+      <c r="S50" s="48">
         <v>2</v>
       </c>
-      <c r="T50" s="6">
-        <v>4</v>
-      </c>
-      <c r="U50" s="6">
+      <c r="T50" s="48">
+        <v>4</v>
+      </c>
+      <c r="U50" s="48">
         <v>2</v>
       </c>
       <c r="V50" s="6">
@@ -39491,16 +39494,16 @@
       <c r="Q51" s="6">
         <v>3</v>
       </c>
-      <c r="R51" s="6">
-        <v>4</v>
-      </c>
-      <c r="S51" s="6">
-        <v>3</v>
-      </c>
-      <c r="T51" s="6">
-        <v>4</v>
-      </c>
-      <c r="U51" s="6">
+      <c r="R51" s="48">
+        <v>4</v>
+      </c>
+      <c r="S51" s="48">
+        <v>3</v>
+      </c>
+      <c r="T51" s="48">
+        <v>4</v>
+      </c>
+      <c r="U51" s="48">
         <v>4</v>
       </c>
       <c r="V51" s="6">
@@ -39580,16 +39583,16 @@
       <c r="Q52" s="6">
         <v>0</v>
       </c>
-      <c r="R52" s="6">
-        <v>4</v>
-      </c>
-      <c r="S52" s="6">
-        <v>4</v>
-      </c>
-      <c r="T52" s="6">
-        <v>3</v>
-      </c>
-      <c r="U52" s="6">
+      <c r="R52" s="48">
+        <v>4</v>
+      </c>
+      <c r="S52" s="48">
+        <v>4</v>
+      </c>
+      <c r="T52" s="48">
+        <v>3</v>
+      </c>
+      <c r="U52" s="48">
         <v>3</v>
       </c>
       <c r="V52" s="6">
@@ -39669,16 +39672,16 @@
       <c r="Q53" s="6">
         <v>3</v>
       </c>
-      <c r="R53" s="6">
+      <c r="R53" s="48">
         <v>2</v>
       </c>
-      <c r="S53" s="6">
+      <c r="S53" s="48">
         <v>2</v>
       </c>
-      <c r="T53" s="6">
-        <v>3</v>
-      </c>
-      <c r="U53" s="6">
+      <c r="T53" s="48">
+        <v>3</v>
+      </c>
+      <c r="U53" s="48">
         <v>3</v>
       </c>
       <c r="V53" s="6">
@@ -39758,16 +39761,16 @@
       <c r="Q54" s="6">
         <v>2</v>
       </c>
-      <c r="R54" s="6">
-        <v>3</v>
-      </c>
-      <c r="S54" s="6">
-        <v>3</v>
-      </c>
-      <c r="T54" s="6">
-        <v>3</v>
-      </c>
-      <c r="U54" s="6">
+      <c r="R54" s="48">
+        <v>3</v>
+      </c>
+      <c r="S54" s="48">
+        <v>3</v>
+      </c>
+      <c r="T54" s="48">
+        <v>3</v>
+      </c>
+      <c r="U54" s="48">
         <v>3</v>
       </c>
       <c r="V54" s="6">
@@ -39847,16 +39850,16 @@
       <c r="Q55" s="6">
         <v>2</v>
       </c>
-      <c r="R55" s="6">
+      <c r="R55" s="48">
         <v>5</v>
       </c>
-      <c r="S55" s="6">
+      <c r="S55" s="48">
         <v>5</v>
       </c>
-      <c r="T55" s="6">
-        <v>4</v>
-      </c>
-      <c r="U55" s="6">
+      <c r="T55" s="48">
+        <v>4</v>
+      </c>
+      <c r="U55" s="48">
         <v>4</v>
       </c>
       <c r="V55" s="6">
@@ -39936,16 +39939,16 @@
       <c r="Q56" s="6">
         <v>3</v>
       </c>
-      <c r="R56" s="6">
-        <v>4</v>
-      </c>
-      <c r="S56" s="6">
-        <v>4</v>
-      </c>
-      <c r="T56" s="6">
+      <c r="R56" s="48">
+        <v>4</v>
+      </c>
+      <c r="S56" s="48">
+        <v>4</v>
+      </c>
+      <c r="T56" s="48">
         <v>5</v>
       </c>
-      <c r="U56" s="6">
+      <c r="U56" s="48">
         <v>2</v>
       </c>
       <c r="V56" s="6">
@@ -40025,16 +40028,16 @@
       <c r="Q57" s="6">
         <v>3</v>
       </c>
-      <c r="R57" s="6">
+      <c r="R57" s="48">
         <v>2</v>
       </c>
-      <c r="S57" s="6">
-        <v>3</v>
-      </c>
-      <c r="T57" s="6">
-        <v>4</v>
-      </c>
-      <c r="U57" s="6">
+      <c r="S57" s="48">
+        <v>3</v>
+      </c>
+      <c r="T57" s="48">
+        <v>4</v>
+      </c>
+      <c r="U57" s="48">
         <v>4</v>
       </c>
       <c r="V57" s="6">
@@ -40114,16 +40117,16 @@
       <c r="Q58" s="6">
         <v>3</v>
       </c>
-      <c r="R58" s="6">
-        <v>3</v>
-      </c>
-      <c r="S58" s="6">
-        <v>3</v>
-      </c>
-      <c r="T58" s="6">
-        <v>3</v>
-      </c>
-      <c r="U58" s="6">
+      <c r="R58" s="48">
+        <v>3</v>
+      </c>
+      <c r="S58" s="48">
+        <v>3</v>
+      </c>
+      <c r="T58" s="48">
+        <v>3</v>
+      </c>
+      <c r="U58" s="48">
         <v>3</v>
       </c>
       <c r="V58" s="6">
@@ -40203,16 +40206,16 @@
       <c r="Q59" s="6">
         <v>2</v>
       </c>
-      <c r="R59" s="6">
+      <c r="R59" s="48">
         <v>2</v>
       </c>
-      <c r="S59" s="6">
-        <v>3</v>
-      </c>
-      <c r="T59" s="6">
-        <v>3</v>
-      </c>
-      <c r="U59" s="6">
+      <c r="S59" s="48">
+        <v>3</v>
+      </c>
+      <c r="T59" s="48">
+        <v>3</v>
+      </c>
+      <c r="U59" s="48">
         <v>3</v>
       </c>
       <c r="V59" s="6">
@@ -40292,16 +40295,16 @@
       <c r="Q60" s="6">
         <v>3</v>
       </c>
-      <c r="R60" s="6">
-        <v>4</v>
-      </c>
-      <c r="S60" s="6">
-        <v>4</v>
-      </c>
-      <c r="T60" s="6">
-        <v>3</v>
-      </c>
-      <c r="U60" s="6">
+      <c r="R60" s="48">
+        <v>4</v>
+      </c>
+      <c r="S60" s="48">
+        <v>4</v>
+      </c>
+      <c r="T60" s="48">
+        <v>3</v>
+      </c>
+      <c r="U60" s="48">
         <v>3</v>
       </c>
       <c r="V60" s="6">
@@ -40381,16 +40384,16 @@
       <c r="Q61" s="6">
         <v>1</v>
       </c>
-      <c r="R61" s="6">
-        <v>3</v>
-      </c>
-      <c r="S61" s="6">
-        <v>4</v>
-      </c>
-      <c r="T61" s="6">
-        <v>4</v>
-      </c>
-      <c r="U61" s="6">
+      <c r="R61" s="48">
+        <v>3</v>
+      </c>
+      <c r="S61" s="48">
+        <v>4</v>
+      </c>
+      <c r="T61" s="48">
+        <v>4</v>
+      </c>
+      <c r="U61" s="48">
         <v>4</v>
       </c>
       <c r="V61" s="6">
@@ -40470,16 +40473,16 @@
       <c r="Q62" s="6">
         <v>2</v>
       </c>
-      <c r="R62" s="6">
-        <v>4</v>
-      </c>
-      <c r="S62" s="6">
-        <v>4</v>
-      </c>
-      <c r="T62" s="6">
-        <v>4</v>
-      </c>
-      <c r="U62" s="6">
+      <c r="R62" s="48">
+        <v>4</v>
+      </c>
+      <c r="S62" s="48">
+        <v>4</v>
+      </c>
+      <c r="T62" s="48">
+        <v>4</v>
+      </c>
+      <c r="U62" s="48">
         <v>5</v>
       </c>
       <c r="V62" s="6">
@@ -40559,16 +40562,16 @@
       <c r="Q63" s="6">
         <v>4</v>
       </c>
-      <c r="R63" s="6">
+      <c r="R63" s="48">
         <v>2</v>
       </c>
-      <c r="S63" s="6">
-        <v>3</v>
-      </c>
-      <c r="T63" s="6">
-        <v>4</v>
-      </c>
-      <c r="U63" s="6">
+      <c r="S63" s="48">
+        <v>3</v>
+      </c>
+      <c r="T63" s="48">
+        <v>4</v>
+      </c>
+      <c r="U63" s="48">
         <v>4</v>
       </c>
       <c r="V63" s="6">
@@ -40648,16 +40651,16 @@
       <c r="Q64" s="6">
         <v>4</v>
       </c>
-      <c r="R64" s="6">
-        <v>4</v>
-      </c>
-      <c r="S64" s="6">
+      <c r="R64" s="48">
+        <v>4</v>
+      </c>
+      <c r="S64" s="48">
         <v>5</v>
       </c>
-      <c r="T64" s="6">
+      <c r="T64" s="48">
         <v>5</v>
       </c>
-      <c r="U64" s="6">
+      <c r="U64" s="48">
         <v>5</v>
       </c>
       <c r="V64" s="6">
@@ -40737,16 +40740,16 @@
       <c r="Q65" s="6">
         <v>1</v>
       </c>
-      <c r="R65" s="6">
+      <c r="R65" s="48">
         <v>2</v>
       </c>
-      <c r="S65" s="6">
-        <v>3</v>
-      </c>
-      <c r="T65" s="6">
-        <v>4</v>
-      </c>
-      <c r="U65" s="6">
+      <c r="S65" s="48">
+        <v>3</v>
+      </c>
+      <c r="T65" s="48">
+        <v>4</v>
+      </c>
+      <c r="U65" s="48">
         <v>0</v>
       </c>
       <c r="V65" s="6">
@@ -40826,16 +40829,16 @@
       <c r="Q66" s="6">
         <v>4</v>
       </c>
-      <c r="R66" s="6">
-        <v>4</v>
-      </c>
-      <c r="S66" s="6">
+      <c r="R66" s="48">
+        <v>4</v>
+      </c>
+      <c r="S66" s="48">
         <v>2</v>
       </c>
-      <c r="T66" s="6">
-        <v>3</v>
-      </c>
-      <c r="U66" s="6">
+      <c r="T66" s="48">
+        <v>3</v>
+      </c>
+      <c r="U66" s="48">
         <v>1</v>
       </c>
       <c r="V66" s="6">
@@ -40915,16 +40918,16 @@
       <c r="Q67" s="6">
         <v>1</v>
       </c>
-      <c r="R67" s="6">
-        <v>4</v>
-      </c>
-      <c r="S67" s="6">
-        <v>3</v>
-      </c>
-      <c r="T67" s="6">
-        <v>4</v>
-      </c>
-      <c r="U67" s="6">
+      <c r="R67" s="48">
+        <v>4</v>
+      </c>
+      <c r="S67" s="48">
+        <v>3</v>
+      </c>
+      <c r="T67" s="48">
+        <v>4</v>
+      </c>
+      <c r="U67" s="48">
         <v>3</v>
       </c>
       <c r="V67" s="6">
@@ -41004,16 +41007,16 @@
       <c r="Q68" s="6">
         <v>5</v>
       </c>
-      <c r="R68" s="6">
+      <c r="R68" s="48">
         <v>5</v>
       </c>
-      <c r="S68" s="6">
-        <v>3</v>
-      </c>
-      <c r="T68" s="6">
+      <c r="S68" s="48">
+        <v>3</v>
+      </c>
+      <c r="T68" s="48">
         <v>5</v>
       </c>
-      <c r="U68" s="6">
+      <c r="U68" s="48">
         <v>4</v>
       </c>
       <c r="V68" s="6">
@@ -41093,16 +41096,16 @@
       <c r="Q69" s="6">
         <v>4</v>
       </c>
-      <c r="R69" s="6">
-        <v>4</v>
-      </c>
-      <c r="S69" s="6">
-        <v>3</v>
-      </c>
-      <c r="T69" s="6">
-        <v>4</v>
-      </c>
-      <c r="U69" s="6">
+      <c r="R69" s="48">
+        <v>4</v>
+      </c>
+      <c r="S69" s="48">
+        <v>3</v>
+      </c>
+      <c r="T69" s="48">
+        <v>4</v>
+      </c>
+      <c r="U69" s="48">
         <v>4</v>
       </c>
       <c r="V69" s="6">
@@ -41182,16 +41185,16 @@
       <c r="Q70" s="6">
         <v>3</v>
       </c>
-      <c r="R70" s="6">
-        <v>3</v>
-      </c>
-      <c r="S70" s="6">
-        <v>3</v>
-      </c>
-      <c r="T70" s="6">
-        <v>3</v>
-      </c>
-      <c r="U70" s="6">
+      <c r="R70" s="48">
+        <v>3</v>
+      </c>
+      <c r="S70" s="48">
+        <v>3</v>
+      </c>
+      <c r="T70" s="48">
+        <v>3</v>
+      </c>
+      <c r="U70" s="48">
         <v>3</v>
       </c>
       <c r="V70" s="6">
@@ -41271,16 +41274,16 @@
       <c r="Q71" s="6">
         <v>4</v>
       </c>
-      <c r="R71" s="6">
+      <c r="R71" s="48">
         <v>5</v>
       </c>
-      <c r="S71" s="6">
-        <v>3</v>
-      </c>
-      <c r="T71" s="6">
+      <c r="S71" s="48">
+        <v>3</v>
+      </c>
+      <c r="T71" s="48">
         <v>2</v>
       </c>
-      <c r="U71" s="6">
+      <c r="U71" s="48">
         <v>4</v>
       </c>
       <c r="V71" s="6">
@@ -41360,16 +41363,16 @@
       <c r="Q72" s="6">
         <v>3</v>
       </c>
-      <c r="R72" s="6">
-        <v>3</v>
-      </c>
-      <c r="S72" s="6">
-        <v>3</v>
-      </c>
-      <c r="T72" s="6">
-        <v>3</v>
-      </c>
-      <c r="U72" s="6">
+      <c r="R72" s="48">
+        <v>3</v>
+      </c>
+      <c r="S72" s="48">
+        <v>3</v>
+      </c>
+      <c r="T72" s="48">
+        <v>3</v>
+      </c>
+      <c r="U72" s="48">
         <v>3</v>
       </c>
       <c r="V72" s="6">
@@ -41449,16 +41452,16 @@
       <c r="Q73" s="6">
         <v>2</v>
       </c>
-      <c r="R73" s="6">
-        <v>3</v>
-      </c>
-      <c r="S73" s="6">
-        <v>4</v>
-      </c>
-      <c r="T73" s="6">
-        <v>4</v>
-      </c>
-      <c r="U73" s="6">
+      <c r="R73" s="48">
+        <v>3</v>
+      </c>
+      <c r="S73" s="48">
+        <v>4</v>
+      </c>
+      <c r="T73" s="48">
+        <v>4</v>
+      </c>
+      <c r="U73" s="48">
         <v>3</v>
       </c>
       <c r="V73" s="6">
@@ -41538,16 +41541,16 @@
       <c r="Q74" s="6">
         <v>4</v>
       </c>
-      <c r="R74" s="6">
-        <v>4</v>
-      </c>
-      <c r="S74" s="6">
-        <v>4</v>
-      </c>
-      <c r="T74" s="6">
-        <v>4</v>
-      </c>
-      <c r="U74" s="6">
+      <c r="R74" s="48">
+        <v>4</v>
+      </c>
+      <c r="S74" s="48">
+        <v>4</v>
+      </c>
+      <c r="T74" s="48">
+        <v>4</v>
+      </c>
+      <c r="U74" s="48">
         <v>4</v>
       </c>
       <c r="V74" s="6">
@@ -41627,16 +41630,16 @@
       <c r="Q75" s="6">
         <v>1</v>
       </c>
-      <c r="R75" s="6">
+      <c r="R75" s="48">
         <v>5</v>
       </c>
-      <c r="S75" s="6">
-        <v>3</v>
-      </c>
-      <c r="T75" s="6">
+      <c r="S75" s="48">
+        <v>3</v>
+      </c>
+      <c r="T75" s="48">
         <v>5</v>
       </c>
-      <c r="U75" s="6">
+      <c r="U75" s="48">
         <v>3</v>
       </c>
       <c r="V75" s="6">
@@ -41716,16 +41719,16 @@
       <c r="Q76" s="6">
         <v>3</v>
       </c>
-      <c r="R76" s="6">
-        <v>4</v>
-      </c>
-      <c r="S76" s="6">
-        <v>3</v>
-      </c>
-      <c r="T76" s="6">
-        <v>4</v>
-      </c>
-      <c r="U76" s="6">
+      <c r="R76" s="48">
+        <v>4</v>
+      </c>
+      <c r="S76" s="48">
+        <v>3</v>
+      </c>
+      <c r="T76" s="48">
+        <v>4</v>
+      </c>
+      <c r="U76" s="48">
         <v>3</v>
       </c>
       <c r="V76" s="6">
@@ -41805,16 +41808,16 @@
       <c r="Q77" s="6">
         <v>2</v>
       </c>
-      <c r="R77" s="6">
-        <v>4</v>
-      </c>
-      <c r="S77" s="6">
-        <v>3</v>
-      </c>
-      <c r="T77" s="6">
+      <c r="R77" s="48">
+        <v>4</v>
+      </c>
+      <c r="S77" s="48">
+        <v>3</v>
+      </c>
+      <c r="T77" s="48">
         <v>5</v>
       </c>
-      <c r="U77" s="6">
+      <c r="U77" s="48">
         <v>4</v>
       </c>
       <c r="V77" s="6">
@@ -41894,16 +41897,16 @@
       <c r="Q78" s="6">
         <v>2</v>
       </c>
-      <c r="R78" s="6">
-        <v>4</v>
-      </c>
-      <c r="S78" s="6">
-        <v>3</v>
-      </c>
-      <c r="T78" s="6">
+      <c r="R78" s="48">
+        <v>4</v>
+      </c>
+      <c r="S78" s="48">
+        <v>3</v>
+      </c>
+      <c r="T78" s="48">
         <v>5</v>
       </c>
-      <c r="U78" s="6">
+      <c r="U78" s="48">
         <v>3</v>
       </c>
       <c r="V78" s="6">
@@ -41983,16 +41986,16 @@
       <c r="Q79" s="6">
         <v>2</v>
       </c>
-      <c r="R79">
-        <v>4</v>
-      </c>
-      <c r="S79">
-        <v>4</v>
-      </c>
-      <c r="T79">
-        <v>4</v>
-      </c>
-      <c r="U79">
+      <c r="R79" s="11">
+        <v>4</v>
+      </c>
+      <c r="S79" s="11">
+        <v>4</v>
+      </c>
+      <c r="T79" s="11">
+        <v>4</v>
+      </c>
+      <c r="U79" s="11">
         <v>4</v>
       </c>
       <c r="V79">
@@ -42072,16 +42075,16 @@
       <c r="Q80" s="6">
         <v>2</v>
       </c>
-      <c r="R80" s="6">
+      <c r="R80" s="48">
         <v>5</v>
       </c>
-      <c r="S80" s="6">
-        <v>4</v>
-      </c>
-      <c r="T80" s="6">
+      <c r="S80" s="48">
+        <v>4</v>
+      </c>
+      <c r="T80" s="48">
         <v>5</v>
       </c>
-      <c r="U80" s="6">
+      <c r="U80" s="48">
         <v>3</v>
       </c>
       <c r="V80" s="6">
@@ -42161,16 +42164,16 @@
       <c r="Q81" s="6">
         <v>1</v>
       </c>
-      <c r="R81" s="6">
+      <c r="R81" s="48">
         <v>5</v>
       </c>
-      <c r="S81" s="6">
+      <c r="S81" s="48">
         <v>5</v>
       </c>
-      <c r="T81" s="6">
+      <c r="T81" s="48">
         <v>5</v>
       </c>
-      <c r="U81" s="6">
+      <c r="U81" s="48">
         <v>5</v>
       </c>
       <c r="V81" s="6">
@@ -42250,16 +42253,16 @@
       <c r="Q82" s="6">
         <v>2</v>
       </c>
-      <c r="R82" s="6">
+      <c r="R82" s="48">
         <v>5</v>
       </c>
-      <c r="S82" s="6">
+      <c r="S82" s="48">
         <v>5</v>
       </c>
-      <c r="T82" s="6">
+      <c r="T82" s="48">
         <v>5</v>
       </c>
-      <c r="U82" s="6">
+      <c r="U82" s="48">
         <v>4</v>
       </c>
       <c r="V82" s="6">
@@ -42339,16 +42342,16 @@
       <c r="Q83" s="6">
         <v>2</v>
       </c>
-      <c r="R83" s="6">
-        <v>4</v>
-      </c>
-      <c r="S83" s="6">
-        <v>4</v>
-      </c>
-      <c r="T83" s="6">
-        <v>4</v>
-      </c>
-      <c r="U83" s="6">
+      <c r="R83" s="48">
+        <v>4</v>
+      </c>
+      <c r="S83" s="48">
+        <v>4</v>
+      </c>
+      <c r="T83" s="48">
+        <v>4</v>
+      </c>
+      <c r="U83" s="48">
         <v>4</v>
       </c>
       <c r="V83" s="6">
@@ -42428,16 +42431,16 @@
       <c r="Q84" s="6">
         <v>5</v>
       </c>
-      <c r="R84" s="6">
-        <v>4</v>
-      </c>
-      <c r="S84" s="6">
-        <v>4</v>
-      </c>
-      <c r="T84" s="6">
-        <v>4</v>
-      </c>
-      <c r="U84" s="6">
+      <c r="R84" s="48">
+        <v>4</v>
+      </c>
+      <c r="S84" s="48">
+        <v>4</v>
+      </c>
+      <c r="T84" s="48">
+        <v>4</v>
+      </c>
+      <c r="U84" s="48">
         <v>4</v>
       </c>
       <c r="V84" s="6">
@@ -42517,16 +42520,16 @@
       <c r="Q85" s="6">
         <v>3</v>
       </c>
-      <c r="R85" s="6">
-        <v>4</v>
-      </c>
-      <c r="S85" s="6">
-        <v>4</v>
-      </c>
-      <c r="T85" s="6">
+      <c r="R85" s="48">
+        <v>4</v>
+      </c>
+      <c r="S85" s="48">
+        <v>4</v>
+      </c>
+      <c r="T85" s="48">
         <v>5</v>
       </c>
-      <c r="U85" s="6">
+      <c r="U85" s="48">
         <v>4</v>
       </c>
       <c r="V85" s="6">
@@ -42606,16 +42609,16 @@
       <c r="Q86" s="6">
         <v>2</v>
       </c>
-      <c r="R86" s="6">
+      <c r="R86" s="48">
         <v>2</v>
       </c>
-      <c r="S86" s="6">
+      <c r="S86" s="48">
         <v>2</v>
       </c>
-      <c r="T86" s="6">
-        <v>4</v>
-      </c>
-      <c r="U86" s="6">
+      <c r="T86" s="48">
+        <v>4</v>
+      </c>
+      <c r="U86" s="48">
         <v>4</v>
       </c>
       <c r="V86" s="6">
@@ -42695,16 +42698,16 @@
       <c r="Q87" s="6">
         <v>4</v>
       </c>
-      <c r="R87" s="6">
+      <c r="R87" s="48">
         <v>2</v>
       </c>
-      <c r="S87" s="6">
-        <v>3</v>
-      </c>
-      <c r="T87" s="6">
-        <v>3</v>
-      </c>
-      <c r="U87" s="6">
+      <c r="S87" s="48">
+        <v>3</v>
+      </c>
+      <c r="T87" s="48">
+        <v>3</v>
+      </c>
+      <c r="U87" s="48">
         <v>2</v>
       </c>
       <c r="V87" s="6">
@@ -42784,16 +42787,16 @@
       <c r="Q88" s="6">
         <v>0</v>
       </c>
-      <c r="R88" s="6">
+      <c r="R88" s="48">
         <v>0</v>
       </c>
-      <c r="S88" s="6">
+      <c r="S88" s="48">
         <v>0</v>
       </c>
-      <c r="T88" s="6">
+      <c r="T88" s="48">
         <v>0</v>
       </c>
-      <c r="U88" s="6">
+      <c r="U88" s="48">
         <v>0</v>
       </c>
       <c r="V88" s="6">
@@ -42873,16 +42876,16 @@
       <c r="Q89" s="6">
         <v>2</v>
       </c>
-      <c r="R89" s="6">
-        <v>4</v>
-      </c>
-      <c r="S89" s="6">
+      <c r="R89" s="48">
+        <v>4</v>
+      </c>
+      <c r="S89" s="48">
         <v>5</v>
       </c>
-      <c r="T89" s="6">
+      <c r="T89" s="48">
         <v>5</v>
       </c>
-      <c r="U89" s="6">
+      <c r="U89" s="48">
         <v>5</v>
       </c>
       <c r="V89" s="6">
@@ -42962,16 +42965,16 @@
       <c r="Q90" s="6">
         <v>5</v>
       </c>
-      <c r="R90" s="6">
+      <c r="R90" s="48">
         <v>5</v>
       </c>
-      <c r="S90" s="6">
+      <c r="S90" s="48">
         <v>5</v>
       </c>
-      <c r="T90" s="6">
+      <c r="T90" s="48">
         <v>5</v>
       </c>
-      <c r="U90" s="6">
+      <c r="U90" s="48">
         <v>5</v>
       </c>
       <c r="V90" s="6">
@@ -43051,16 +43054,16 @@
       <c r="Q91" s="6">
         <v>2</v>
       </c>
-      <c r="R91" s="6">
+      <c r="R91" s="48">
         <v>5</v>
       </c>
-      <c r="S91" s="6">
-        <v>4</v>
-      </c>
-      <c r="T91" s="6">
+      <c r="S91" s="48">
+        <v>4</v>
+      </c>
+      <c r="T91" s="48">
         <v>5</v>
       </c>
-      <c r="U91" s="6">
+      <c r="U91" s="48">
         <v>4</v>
       </c>
       <c r="V91" s="6">
@@ -43140,16 +43143,16 @@
       <c r="Q92" s="6">
         <v>1</v>
       </c>
-      <c r="R92" s="6">
-        <v>4</v>
-      </c>
-      <c r="S92" s="6">
+      <c r="R92" s="48">
+        <v>4</v>
+      </c>
+      <c r="S92" s="48">
         <v>5</v>
       </c>
-      <c r="T92" s="6">
+      <c r="T92" s="48">
         <v>5</v>
       </c>
-      <c r="U92" s="6">
+      <c r="U92" s="48">
         <v>5</v>
       </c>
       <c r="V92" s="6">
@@ -43229,16 +43232,16 @@
       <c r="Q93" s="6">
         <v>2</v>
       </c>
-      <c r="R93" s="6">
-        <v>4</v>
-      </c>
-      <c r="S93" s="6">
-        <v>4</v>
-      </c>
-      <c r="T93" s="6">
-        <v>4</v>
-      </c>
-      <c r="U93" s="6">
+      <c r="R93" s="48">
+        <v>4</v>
+      </c>
+      <c r="S93" s="48">
+        <v>4</v>
+      </c>
+      <c r="T93" s="48">
+        <v>4</v>
+      </c>
+      <c r="U93" s="48">
         <v>4</v>
       </c>
       <c r="V93" s="6">
@@ -43318,16 +43321,16 @@
       <c r="Q94" s="6">
         <v>2</v>
       </c>
-      <c r="R94" s="6">
+      <c r="R94" s="48">
         <v>5</v>
       </c>
-      <c r="S94" s="6">
-        <v>3</v>
-      </c>
-      <c r="T94" s="6">
-        <v>4</v>
-      </c>
-      <c r="U94" s="6">
+      <c r="S94" s="48">
+        <v>3</v>
+      </c>
+      <c r="T94" s="48">
+        <v>4</v>
+      </c>
+      <c r="U94" s="48">
         <v>4</v>
       </c>
       <c r="V94" s="6">
@@ -43407,16 +43410,16 @@
       <c r="Q95" s="6">
         <v>3</v>
       </c>
-      <c r="R95" s="6">
-        <v>4</v>
-      </c>
-      <c r="S95" s="6">
-        <v>3</v>
-      </c>
-      <c r="T95" s="6">
-        <v>4</v>
-      </c>
-      <c r="U95" s="6">
+      <c r="R95" s="48">
+        <v>4</v>
+      </c>
+      <c r="S95" s="48">
+        <v>3</v>
+      </c>
+      <c r="T95" s="48">
+        <v>4</v>
+      </c>
+      <c r="U95" s="48">
         <v>3</v>
       </c>
       <c r="V95" s="6">
@@ -43496,16 +43499,16 @@
       <c r="Q96" s="6">
         <v>2</v>
       </c>
-      <c r="R96" s="6">
+      <c r="R96" s="48">
         <v>5</v>
       </c>
-      <c r="S96" s="6">
+      <c r="S96" s="48">
         <v>5</v>
       </c>
-      <c r="T96" s="6">
+      <c r="T96" s="48">
         <v>5</v>
       </c>
-      <c r="U96" s="6">
+      <c r="U96" s="48">
         <v>5</v>
       </c>
       <c r="V96" s="6">
@@ -43585,16 +43588,16 @@
       <c r="Q97" s="6">
         <v>1</v>
       </c>
-      <c r="R97" s="6">
-        <v>4</v>
-      </c>
-      <c r="S97" s="6">
-        <v>4</v>
-      </c>
-      <c r="T97" s="6">
+      <c r="R97" s="48">
+        <v>4</v>
+      </c>
+      <c r="S97" s="48">
+        <v>4</v>
+      </c>
+      <c r="T97" s="48">
         <v>5</v>
       </c>
-      <c r="U97" s="6">
+      <c r="U97" s="48">
         <v>5</v>
       </c>
       <c r="V97" s="6">
@@ -43674,16 +43677,16 @@
       <c r="Q98" s="6">
         <v>2</v>
       </c>
-      <c r="R98" s="6">
-        <v>4</v>
-      </c>
-      <c r="S98" s="6">
-        <v>4</v>
-      </c>
-      <c r="T98" s="6">
+      <c r="R98" s="48">
+        <v>4</v>
+      </c>
+      <c r="S98" s="48">
+        <v>4</v>
+      </c>
+      <c r="T98" s="48">
         <v>5</v>
       </c>
-      <c r="U98" s="6">
+      <c r="U98" s="48">
         <v>4</v>
       </c>
       <c r="V98" s="6">
@@ -43760,16 +43763,16 @@
       <c r="Q99" s="6">
         <v>3</v>
       </c>
-      <c r="R99" s="6">
-        <v>3</v>
-      </c>
-      <c r="S99" s="6">
-        <v>3</v>
-      </c>
-      <c r="T99" s="6">
-        <v>4</v>
-      </c>
-      <c r="U99" s="6">
+      <c r="R99" s="48">
+        <v>3</v>
+      </c>
+      <c r="S99" s="48">
+        <v>3</v>
+      </c>
+      <c r="T99" s="48">
+        <v>4</v>
+      </c>
+      <c r="U99" s="48">
         <v>4</v>
       </c>
       <c r="V99" s="6">
@@ -43849,16 +43852,16 @@
       <c r="Q100" s="6">
         <v>3</v>
       </c>
-      <c r="R100" s="6">
+      <c r="R100" s="48">
         <v>5</v>
       </c>
-      <c r="S100" s="6">
+      <c r="S100" s="48">
         <v>5</v>
       </c>
-      <c r="T100" s="6">
-        <v>4</v>
-      </c>
-      <c r="U100" s="6">
+      <c r="T100" s="48">
+        <v>4</v>
+      </c>
+      <c r="U100" s="48">
         <v>3</v>
       </c>
       <c r="V100" s="6">
@@ -43938,16 +43941,16 @@
       <c r="Q101" s="6">
         <v>2</v>
       </c>
-      <c r="R101" s="6">
-        <v>4</v>
-      </c>
-      <c r="S101" s="6">
+      <c r="R101" s="48">
+        <v>4</v>
+      </c>
+      <c r="S101" s="48">
         <v>5</v>
       </c>
-      <c r="T101" s="6">
+      <c r="T101" s="48">
         <v>5</v>
       </c>
-      <c r="U101" s="6">
+      <c r="U101" s="48">
         <v>4</v>
       </c>
       <c r="V101" s="6">
@@ -44027,16 +44030,16 @@
       <c r="Q102" s="6">
         <v>3</v>
       </c>
-      <c r="R102" s="6">
+      <c r="R102" s="48">
         <v>5</v>
       </c>
-      <c r="S102" s="6">
+      <c r="S102" s="48">
         <v>5</v>
       </c>
-      <c r="T102" s="6">
+      <c r="T102" s="48">
         <v>5</v>
       </c>
-      <c r="U102" s="6">
+      <c r="U102" s="48">
         <v>5</v>
       </c>
       <c r="V102" s="6">
@@ -44116,16 +44119,16 @@
       <c r="Q103" s="6">
         <v>3</v>
       </c>
-      <c r="R103" s="6">
+      <c r="R103" s="48">
         <v>5</v>
       </c>
-      <c r="S103" s="6">
+      <c r="S103" s="48">
         <v>5</v>
       </c>
-      <c r="T103" s="6">
+      <c r="T103" s="48">
         <v>5</v>
       </c>
-      <c r="U103" s="6">
+      <c r="U103" s="48">
         <v>5</v>
       </c>
       <c r="V103" s="6">
@@ -44205,16 +44208,16 @@
       <c r="Q104" s="6">
         <v>2</v>
       </c>
-      <c r="R104" s="6">
+      <c r="R104" s="48">
         <v>5</v>
       </c>
-      <c r="S104" s="6">
-        <v>4</v>
-      </c>
-      <c r="T104" s="6">
+      <c r="S104" s="48">
+        <v>4</v>
+      </c>
+      <c r="T104" s="48">
         <v>5</v>
       </c>
-      <c r="U104" s="6">
+      <c r="U104" s="48">
         <v>5</v>
       </c>
       <c r="V104" s="6">
@@ -44294,16 +44297,16 @@
       <c r="Q105" s="6">
         <v>2</v>
       </c>
-      <c r="R105" s="6">
+      <c r="R105" s="48">
         <v>5</v>
       </c>
-      <c r="S105" s="6">
+      <c r="S105" s="48">
         <v>5</v>
       </c>
-      <c r="T105" s="6">
+      <c r="T105" s="48">
         <v>5</v>
       </c>
-      <c r="U105" s="6">
+      <c r="U105" s="48">
         <v>5</v>
       </c>
       <c r="V105" s="6">
@@ -44383,16 +44386,16 @@
       <c r="Q106" s="6">
         <v>0</v>
       </c>
-      <c r="R106" s="6">
-        <v>4</v>
-      </c>
-      <c r="S106" s="6">
-        <v>4</v>
-      </c>
-      <c r="T106" s="6">
-        <v>4</v>
-      </c>
-      <c r="U106" s="6">
+      <c r="R106" s="48">
+        <v>4</v>
+      </c>
+      <c r="S106" s="48">
+        <v>4</v>
+      </c>
+      <c r="T106" s="48">
+        <v>4</v>
+      </c>
+      <c r="U106" s="48">
         <v>3</v>
       </c>
       <c r="V106" s="6">
@@ -44472,16 +44475,16 @@
       <c r="Q107" s="6">
         <v>1</v>
       </c>
-      <c r="R107" s="6">
+      <c r="R107" s="48">
         <v>5</v>
       </c>
-      <c r="S107" s="6">
+      <c r="S107" s="48">
         <v>0</v>
       </c>
-      <c r="T107" s="6">
-        <v>4</v>
-      </c>
-      <c r="U107" s="6">
+      <c r="T107" s="48">
+        <v>4</v>
+      </c>
+      <c r="U107" s="48">
         <v>5</v>
       </c>
       <c r="V107" s="6">
@@ -44561,16 +44564,16 @@
       <c r="Q108" s="6">
         <v>1</v>
       </c>
-      <c r="R108" s="6">
+      <c r="R108" s="48">
         <v>5</v>
       </c>
-      <c r="S108" s="6">
+      <c r="S108" s="48">
         <v>5</v>
       </c>
-      <c r="T108" s="6">
+      <c r="T108" s="48">
         <v>5</v>
       </c>
-      <c r="U108" s="6">
+      <c r="U108" s="48">
         <v>5</v>
       </c>
       <c r="V108" s="6">
@@ -44650,16 +44653,16 @@
       <c r="Q109" s="6">
         <v>2</v>
       </c>
-      <c r="R109" s="6">
+      <c r="R109" s="48">
         <v>5</v>
       </c>
-      <c r="S109" s="6">
-        <v>4</v>
-      </c>
-      <c r="T109" s="6">
+      <c r="S109" s="48">
+        <v>4</v>
+      </c>
+      <c r="T109" s="48">
         <v>5</v>
       </c>
-      <c r="U109" s="6">
+      <c r="U109" s="48">
         <v>5</v>
       </c>
       <c r="V109" s="6">
@@ -44739,16 +44742,16 @@
       <c r="Q110" s="6">
         <v>2</v>
       </c>
-      <c r="R110" s="6">
+      <c r="R110" s="48">
         <v>5</v>
       </c>
-      <c r="S110" s="6">
-        <v>4</v>
-      </c>
-      <c r="T110" s="6">
+      <c r="S110" s="48">
+        <v>4</v>
+      </c>
+      <c r="T110" s="48">
         <v>5</v>
       </c>
-      <c r="U110" s="6">
+      <c r="U110" s="48">
         <v>5</v>
       </c>
       <c r="V110" s="6">
@@ -44828,16 +44831,16 @@
       <c r="Q111">
         <v>0</v>
       </c>
-      <c r="R111">
+      <c r="R111" s="11">
         <v>0</v>
       </c>
-      <c r="S111">
+      <c r="S111" s="11">
         <v>0</v>
       </c>
-      <c r="T111">
+      <c r="T111" s="11">
         <v>0</v>
       </c>
-      <c r="U111">
+      <c r="U111" s="11">
         <v>0</v>
       </c>
       <c r="V111">
@@ -44917,16 +44920,16 @@
       <c r="Q112" s="6">
         <v>3</v>
       </c>
-      <c r="R112" s="6">
-        <v>3</v>
-      </c>
-      <c r="S112" s="6">
-        <v>3</v>
-      </c>
-      <c r="T112" s="6">
-        <v>3</v>
-      </c>
-      <c r="U112" s="6">
+      <c r="R112" s="48">
+        <v>3</v>
+      </c>
+      <c r="S112" s="48">
+        <v>3</v>
+      </c>
+      <c r="T112" s="48">
+        <v>3</v>
+      </c>
+      <c r="U112" s="48">
         <v>3</v>
       </c>
       <c r="V112" s="6">
@@ -45006,16 +45009,16 @@
       <c r="Q113" s="6">
         <v>1</v>
       </c>
-      <c r="R113" s="6">
-        <v>4</v>
-      </c>
-      <c r="S113" s="6">
-        <v>3</v>
-      </c>
-      <c r="T113" s="6">
-        <v>4</v>
-      </c>
-      <c r="U113" s="6">
+      <c r="R113" s="48">
+        <v>4</v>
+      </c>
+      <c r="S113" s="48">
+        <v>3</v>
+      </c>
+      <c r="T113" s="48">
+        <v>4</v>
+      </c>
+      <c r="U113" s="48">
         <v>4</v>
       </c>
       <c r="V113" s="6">
@@ -45095,16 +45098,16 @@
       <c r="Q114" s="6">
         <v>1</v>
       </c>
-      <c r="R114" s="6">
-        <v>4</v>
-      </c>
-      <c r="S114" s="6">
-        <v>3</v>
-      </c>
-      <c r="T114" s="6">
-        <v>4</v>
-      </c>
-      <c r="U114" s="6">
+      <c r="R114" s="48">
+        <v>4</v>
+      </c>
+      <c r="S114" s="48">
+        <v>3</v>
+      </c>
+      <c r="T114" s="48">
+        <v>4</v>
+      </c>
+      <c r="U114" s="48">
         <v>4</v>
       </c>
       <c r="V114" s="6">
@@ -45184,16 +45187,16 @@
       <c r="Q115" s="6">
         <v>2</v>
       </c>
-      <c r="R115" s="6">
-        <v>3</v>
-      </c>
-      <c r="S115" s="6">
-        <v>3</v>
-      </c>
-      <c r="T115" s="6">
-        <v>4</v>
-      </c>
-      <c r="U115" s="6">
+      <c r="R115" s="48">
+        <v>3</v>
+      </c>
+      <c r="S115" s="48">
+        <v>3</v>
+      </c>
+      <c r="T115" s="48">
+        <v>4</v>
+      </c>
+      <c r="U115" s="48">
         <v>4</v>
       </c>
       <c r="V115" s="6">
@@ -45273,16 +45276,16 @@
       <c r="Q116" s="6">
         <v>1</v>
       </c>
-      <c r="R116" s="6">
-        <v>3</v>
-      </c>
-      <c r="S116" s="6">
-        <v>3</v>
-      </c>
-      <c r="T116" s="6">
-        <v>4</v>
-      </c>
-      <c r="U116" s="6">
+      <c r="R116" s="48">
+        <v>3</v>
+      </c>
+      <c r="S116" s="48">
+        <v>3</v>
+      </c>
+      <c r="T116" s="48">
+        <v>4</v>
+      </c>
+      <c r="U116" s="48">
         <v>4</v>
       </c>
       <c r="V116" s="6">
@@ -45362,16 +45365,16 @@
       <c r="Q117" s="6">
         <v>4</v>
       </c>
-      <c r="R117" s="6">
-        <v>4</v>
-      </c>
-      <c r="S117" s="6">
-        <v>3</v>
-      </c>
-      <c r="T117" s="6">
-        <v>4</v>
-      </c>
-      <c r="U117" s="6">
+      <c r="R117" s="48">
+        <v>4</v>
+      </c>
+      <c r="S117" s="48">
+        <v>3</v>
+      </c>
+      <c r="T117" s="48">
+        <v>4</v>
+      </c>
+      <c r="U117" s="48">
         <v>3</v>
       </c>
       <c r="V117" s="6">
@@ -45451,16 +45454,16 @@
       <c r="Q118" s="6">
         <v>1</v>
       </c>
-      <c r="R118" s="6">
+      <c r="R118" s="48">
         <v>5</v>
       </c>
-      <c r="S118" s="6">
-        <v>3</v>
-      </c>
-      <c r="T118" s="6">
+      <c r="S118" s="48">
+        <v>3</v>
+      </c>
+      <c r="T118" s="48">
         <v>5</v>
       </c>
-      <c r="U118" s="6">
+      <c r="U118" s="48">
         <v>4</v>
       </c>
       <c r="V118" s="6">
@@ -45540,16 +45543,16 @@
       <c r="Q119" s="6">
         <v>3</v>
       </c>
-      <c r="R119" s="6">
-        <v>4</v>
-      </c>
-      <c r="S119" s="6">
-        <v>4</v>
-      </c>
-      <c r="T119" s="6">
-        <v>4</v>
-      </c>
-      <c r="U119" s="6">
+      <c r="R119" s="48">
+        <v>4</v>
+      </c>
+      <c r="S119" s="48">
+        <v>4</v>
+      </c>
+      <c r="T119" s="48">
+        <v>4</v>
+      </c>
+      <c r="U119" s="48">
         <v>3</v>
       </c>
       <c r="V119" s="6">
@@ -45629,16 +45632,16 @@
       <c r="Q120" s="6">
         <v>3</v>
       </c>
-      <c r="R120" s="6">
-        <v>3</v>
-      </c>
-      <c r="S120" s="6">
-        <v>4</v>
-      </c>
-      <c r="T120" s="6">
+      <c r="R120" s="48">
+        <v>3</v>
+      </c>
+      <c r="S120" s="48">
+        <v>4</v>
+      </c>
+      <c r="T120" s="48">
         <v>5</v>
       </c>
-      <c r="U120" s="6">
+      <c r="U120" s="48">
         <v>3</v>
       </c>
       <c r="V120" s="6">
@@ -45718,16 +45721,16 @@
       <c r="Q121" s="6">
         <v>2</v>
       </c>
-      <c r="R121" s="6">
-        <v>4</v>
-      </c>
-      <c r="S121" s="6">
-        <v>4</v>
-      </c>
-      <c r="T121" s="6">
+      <c r="R121" s="48">
+        <v>4</v>
+      </c>
+      <c r="S121" s="48">
+        <v>4</v>
+      </c>
+      <c r="T121" s="48">
         <v>5</v>
       </c>
-      <c r="U121" s="6">
+      <c r="U121" s="48">
         <v>4</v>
       </c>
       <c r="V121" s="6">
@@ -45807,16 +45810,16 @@
       <c r="Q122" s="6">
         <v>4</v>
       </c>
-      <c r="R122" s="6">
+      <c r="R122" s="48">
         <v>2</v>
       </c>
-      <c r="S122" s="6">
-        <v>4</v>
-      </c>
-      <c r="T122" s="6">
-        <v>3</v>
-      </c>
-      <c r="U122" s="6">
+      <c r="S122" s="48">
+        <v>4</v>
+      </c>
+      <c r="T122" s="48">
+        <v>3</v>
+      </c>
+      <c r="U122" s="48">
         <v>3</v>
       </c>
       <c r="V122" s="6">
@@ -45896,16 +45899,16 @@
       <c r="Q123" s="6">
         <v>4</v>
       </c>
-      <c r="R123" s="6">
-        <v>4</v>
-      </c>
-      <c r="S123" s="6">
-        <v>3</v>
-      </c>
-      <c r="T123" s="6">
-        <v>4</v>
-      </c>
-      <c r="U123" s="6">
+      <c r="R123" s="48">
+        <v>4</v>
+      </c>
+      <c r="S123" s="48">
+        <v>3</v>
+      </c>
+      <c r="T123" s="48">
+        <v>4</v>
+      </c>
+      <c r="U123" s="48">
         <v>4</v>
       </c>
       <c r="V123" s="6">
@@ -45985,16 +45988,16 @@
       <c r="Q124" s="6">
         <v>2</v>
       </c>
-      <c r="R124" s="6">
-        <v>4</v>
-      </c>
-      <c r="S124" s="6">
-        <v>4</v>
-      </c>
-      <c r="T124" s="6">
-        <v>4</v>
-      </c>
-      <c r="U124" s="6">
+      <c r="R124" s="48">
+        <v>4</v>
+      </c>
+      <c r="S124" s="48">
+        <v>4</v>
+      </c>
+      <c r="T124" s="48">
+        <v>4</v>
+      </c>
+      <c r="U124" s="48">
         <v>4</v>
       </c>
       <c r="V124" s="6">
@@ -46074,16 +46077,16 @@
       <c r="Q125" s="6">
         <v>3</v>
       </c>
-      <c r="R125" s="6">
-        <v>4</v>
-      </c>
-      <c r="S125" s="6">
-        <v>3</v>
-      </c>
-      <c r="T125" s="6">
-        <v>3</v>
-      </c>
-      <c r="U125" s="6">
+      <c r="R125" s="48">
+        <v>4</v>
+      </c>
+      <c r="S125" s="48">
+        <v>3</v>
+      </c>
+      <c r="T125" s="48">
+        <v>3</v>
+      </c>
+      <c r="U125" s="48">
         <v>1</v>
       </c>
       <c r="V125" s="6">
@@ -46163,16 +46166,16 @@
       <c r="Q126" s="6">
         <v>0</v>
       </c>
-      <c r="R126" s="6">
+      <c r="R126" s="48">
         <v>0</v>
       </c>
-      <c r="S126" s="6">
+      <c r="S126" s="48">
         <v>0</v>
       </c>
-      <c r="T126" s="6">
+      <c r="T126" s="48">
         <v>0</v>
       </c>
-      <c r="U126" s="6">
+      <c r="U126" s="48">
         <v>0</v>
       </c>
       <c r="V126" s="6">
@@ -46252,16 +46255,16 @@
       <c r="Q127" s="6">
         <v>2</v>
       </c>
-      <c r="R127" s="6">
-        <v>4</v>
-      </c>
-      <c r="S127" s="6">
+      <c r="R127" s="48">
+        <v>4</v>
+      </c>
+      <c r="S127" s="48">
         <v>5</v>
       </c>
-      <c r="T127" s="6">
-        <v>4</v>
-      </c>
-      <c r="U127" s="6">
+      <c r="T127" s="48">
+        <v>4</v>
+      </c>
+      <c r="U127" s="48">
         <v>4</v>
       </c>
       <c r="V127" s="6">
@@ -46341,16 +46344,16 @@
       <c r="Q128" s="6">
         <v>2</v>
       </c>
-      <c r="R128" s="6">
-        <v>4</v>
-      </c>
-      <c r="S128" s="6">
+      <c r="R128" s="48">
+        <v>4</v>
+      </c>
+      <c r="S128" s="48">
         <v>5</v>
       </c>
-      <c r="T128" s="6">
-        <v>4</v>
-      </c>
-      <c r="U128" s="6">
+      <c r="T128" s="48">
+        <v>4</v>
+      </c>
+      <c r="U128" s="48">
         <v>2</v>
       </c>
       <c r="V128" s="6">
@@ -46430,16 +46433,16 @@
       <c r="Q129" s="6">
         <v>0</v>
       </c>
-      <c r="R129" s="6">
+      <c r="R129" s="48">
         <v>0</v>
       </c>
-      <c r="S129" s="6">
+      <c r="S129" s="48">
         <v>0</v>
       </c>
-      <c r="T129" s="6">
+      <c r="T129" s="48">
         <v>0</v>
       </c>
-      <c r="U129" s="6">
+      <c r="U129" s="48">
         <v>0</v>
       </c>
       <c r="V129" s="6">
@@ -46519,16 +46522,16 @@
       <c r="Q130" s="6">
         <v>1</v>
       </c>
-      <c r="R130" s="6">
-        <v>4</v>
-      </c>
-      <c r="S130" s="6">
-        <v>4</v>
-      </c>
-      <c r="T130" s="6">
+      <c r="R130" s="48">
+        <v>4</v>
+      </c>
+      <c r="S130" s="48">
+        <v>4</v>
+      </c>
+      <c r="T130" s="48">
         <v>5</v>
       </c>
-      <c r="U130" s="6">
+      <c r="U130" s="48">
         <v>5</v>
       </c>
       <c r="V130" s="6">
@@ -46608,16 +46611,16 @@
       <c r="Q131" s="6">
         <v>1</v>
       </c>
-      <c r="R131" s="6">
+      <c r="R131" s="48">
         <v>5</v>
       </c>
-      <c r="S131" s="6">
+      <c r="S131" s="48">
         <v>5</v>
       </c>
-      <c r="T131" s="6">
+      <c r="T131" s="48">
         <v>5</v>
       </c>
-      <c r="U131" s="6">
+      <c r="U131" s="48">
         <v>5</v>
       </c>
       <c r="V131" s="6">
